--- a/research/traditional_assets/database/data/jordan/jordan_household_products.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_household_products.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.107589198630598</v>
+        <v>0.1074100202333368</v>
       </c>
       <c r="C2">
-        <v>32.38604472371202</v>
+        <v>32.17501500598431</v>
       </c>
       <c r="D2">
-        <v>30.93604472371202</v>
+        <v>31.02601500598432</v>
       </c>
       <c r="E2">
-        <v>-12.6</v>
+        <v>-12.299</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.301</v>
       </c>
       <c r="G2">
         <v>1.45</v>
@@ -1451,28 +1451,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0151403</v>
       </c>
       <c r="N2">
-        <v>3.074444444444444</v>
+        <v>3.059304144444444</v>
       </c>
       <c r="O2">
-        <v>0.6148888888888888</v>
+        <v>0.6118608288888888</v>
       </c>
       <c r="P2">
-        <v>2.459555555555555</v>
+        <v>2.447443315555555</v>
       </c>
       <c r="Q2">
-        <v>3.429555555555555</v>
+        <v>3.417443315555555</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.107589198630598</v>
+        <v>0.1080885052861988</v>
       </c>
       <c r="T2">
-        <v>0.6766170509100436</v>
+        <v>0.6820846634426501</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>203.0636410404314</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1074100202333368</v>
+        <v>0.1072308418360757</v>
       </c>
       <c r="C3">
-        <v>32.17501500598431</v>
+        <v>31.96451012986701</v>
       </c>
       <c r="D3">
-        <v>31.02601500598432</v>
+        <v>31.11651012986701</v>
       </c>
       <c r="E3">
-        <v>-12.299</v>
+        <v>-11.998</v>
       </c>
       <c r="F3">
-        <v>0.301</v>
+        <v>0.6020000000000001</v>
       </c>
       <c r="G3">
         <v>1.45</v>
@@ -1533,28 +1533,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M3">
-        <v>0.0151403</v>
+        <v>0.0302806</v>
       </c>
       <c r="N3">
-        <v>3.059304144444444</v>
+        <v>3.044163844444444</v>
       </c>
       <c r="O3">
-        <v>0.6118608288888888</v>
+        <v>0.6088327688888888</v>
       </c>
       <c r="P3">
-        <v>2.447443315555555</v>
+        <v>2.435331075555555</v>
       </c>
       <c r="Q3">
-        <v>3.417443315555555</v>
+        <v>3.405331075555555</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1080885052861988</v>
+        <v>0.1085980018735466</v>
       </c>
       <c r="T3">
-        <v>0.6820846634426501</v>
+        <v>0.6876638599044933</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>203.0636410404314</v>
+        <v>101.5318205202157</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1072308418360757</v>
+        <v>0.1070516634388145</v>
       </c>
       <c r="C4">
-        <v>31.96451012986701</v>
+        <v>31.75453470128948</v>
       </c>
       <c r="D4">
-        <v>31.11651012986701</v>
+        <v>31.20753470128948</v>
       </c>
       <c r="E4">
-        <v>-11.998</v>
+        <v>-11.697</v>
       </c>
       <c r="F4">
-        <v>0.6020000000000001</v>
+        <v>0.903</v>
       </c>
       <c r="G4">
         <v>1.45</v>
@@ -1615,28 +1615,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M4">
-        <v>0.0302806</v>
+        <v>0.0454209</v>
       </c>
       <c r="N4">
-        <v>3.044163844444444</v>
+        <v>3.029023544444444</v>
       </c>
       <c r="O4">
-        <v>0.6088327688888888</v>
+        <v>0.6058047088888889</v>
       </c>
       <c r="P4">
-        <v>2.435331075555555</v>
+        <v>2.423218835555555</v>
       </c>
       <c r="Q4">
-        <v>3.405331075555555</v>
+        <v>3.393218835555555</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1085980018735466</v>
+        <v>0.1091180035451695</v>
       </c>
       <c r="T4">
-        <v>0.6876638599044933</v>
+        <v>0.6933580913449313</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>101.5318205202157</v>
+        <v>67.68788034681049</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1070516634388145</v>
+        <v>0.1068724850415533</v>
       </c>
       <c r="C5">
-        <v>31.75453470128948</v>
+        <v>31.54509338023377</v>
       </c>
       <c r="D5">
-        <v>31.20753470128948</v>
+        <v>31.29909338023377</v>
       </c>
       <c r="E5">
-        <v>-11.697</v>
+        <v>-11.396</v>
       </c>
       <c r="F5">
-        <v>0.903</v>
+        <v>1.204</v>
       </c>
       <c r="G5">
         <v>1.45</v>
@@ -1697,28 +1697,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M5">
-        <v>0.0454209</v>
+        <v>0.06056120000000001</v>
       </c>
       <c r="N5">
-        <v>3.029023544444444</v>
+        <v>3.013883244444444</v>
       </c>
       <c r="O5">
-        <v>0.6058047088888889</v>
+        <v>0.6027766488888888</v>
       </c>
       <c r="P5">
-        <v>2.423218835555555</v>
+        <v>2.411106595555555</v>
       </c>
       <c r="Q5">
-        <v>3.393218835555555</v>
+        <v>3.381106595555555</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1091180035451695</v>
+        <v>0.1096488385849513</v>
       </c>
       <c r="T5">
-        <v>0.6933580913449313</v>
+        <v>0.6991709526070452</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>67.68788034681049</v>
+        <v>50.76591026010785</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1068724850415533</v>
+        <v>0.1066933066442921</v>
       </c>
       <c r="C6">
-        <v>31.54509338023377</v>
+        <v>31.33619088152992</v>
       </c>
       <c r="D6">
-        <v>31.29909338023377</v>
+        <v>31.39119088152992</v>
       </c>
       <c r="E6">
-        <v>-11.396</v>
+        <v>-11.095</v>
       </c>
       <c r="F6">
-        <v>1.204</v>
+        <v>1.505</v>
       </c>
       <c r="G6">
         <v>1.45</v>
@@ -1779,28 +1779,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M6">
-        <v>0.06056120000000001</v>
+        <v>0.0757015</v>
       </c>
       <c r="N6">
-        <v>3.013883244444444</v>
+        <v>2.998742944444444</v>
       </c>
       <c r="O6">
-        <v>0.6027766488888888</v>
+        <v>0.5997485888888888</v>
       </c>
       <c r="P6">
-        <v>2.411106595555555</v>
+        <v>2.398994355555555</v>
       </c>
       <c r="Q6">
-        <v>3.381106595555555</v>
+        <v>3.368994355555555</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1096488385849513</v>
+        <v>0.1101908490992548</v>
       </c>
       <c r="T6">
-        <v>0.6991709526070452</v>
+        <v>0.7051061898957296</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>50.76591026010785</v>
+        <v>40.61272820808628</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1066933066442921</v>
+        <v>0.1065141282470309</v>
       </c>
       <c r="C7">
-        <v>31.33619088152992</v>
+        <v>31.12783197566518</v>
       </c>
       <c r="D7">
-        <v>31.39119088152992</v>
+        <v>31.48383197566518</v>
       </c>
       <c r="E7">
-        <v>-11.095</v>
+        <v>-10.794</v>
       </c>
       <c r="F7">
-        <v>1.505</v>
+        <v>1.806</v>
       </c>
       <c r="G7">
         <v>1.45</v>
@@ -1861,28 +1861,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M7">
-        <v>0.0757015</v>
+        <v>0.09084180000000001</v>
       </c>
       <c r="N7">
-        <v>2.998742944444444</v>
+        <v>2.983602644444444</v>
       </c>
       <c r="O7">
-        <v>0.5997485888888888</v>
+        <v>0.5967205288888888</v>
       </c>
       <c r="P7">
-        <v>2.398994355555555</v>
+        <v>2.386882115555555</v>
       </c>
       <c r="Q7">
-        <v>3.368994355555555</v>
+        <v>3.356882115555555</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1101908490992548</v>
+        <v>0.1107443917521605</v>
       </c>
       <c r="T7">
-        <v>0.7051061898957296</v>
+        <v>0.7111677088288544</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>40.61272820808628</v>
+        <v>33.84394017340523</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1065141282470309</v>
+        <v>0.1063349498497697</v>
       </c>
       <c r="C8">
-        <v>31.12783197566518</v>
+        <v>30.92002148960778</v>
       </c>
       <c r="D8">
-        <v>31.48383197566518</v>
+        <v>31.57702148960778</v>
       </c>
       <c r="E8">
-        <v>-10.794</v>
+        <v>-10.493</v>
       </c>
       <c r="F8">
-        <v>1.806</v>
+        <v>2.107</v>
       </c>
       <c r="G8">
         <v>1.45</v>
@@ -1943,28 +1943,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M8">
-        <v>0.0908418</v>
+        <v>0.1059821</v>
       </c>
       <c r="N8">
-        <v>2.983602644444444</v>
+        <v>2.968462344444444</v>
       </c>
       <c r="O8">
-        <v>0.5967205288888888</v>
+        <v>0.5936924688888888</v>
       </c>
       <c r="P8">
-        <v>2.386882115555555</v>
+        <v>2.374769875555555</v>
       </c>
       <c r="Q8">
-        <v>3.356882115555555</v>
+        <v>3.344769875555555</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1107443917521605</v>
+        <v>0.1113098385481394</v>
       </c>
       <c r="T8">
-        <v>0.7111677088288544</v>
+        <v>0.7173595830078527</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>33.84394017340524</v>
+        <v>29.0090915772045</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1063349498497697</v>
+        <v>0.1061557714525085</v>
       </c>
       <c r="C9">
-        <v>30.92002148960778</v>
+        <v>30.71276430764535</v>
       </c>
       <c r="D9">
-        <v>31.57702148960778</v>
+        <v>31.67076430764535</v>
       </c>
       <c r="E9">
-        <v>-10.493</v>
+        <v>-10.192</v>
       </c>
       <c r="F9">
-        <v>2.107</v>
+        <v>2.408</v>
       </c>
       <c r="G9">
         <v>1.45</v>
@@ -2025,28 +2025,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M9">
-        <v>0.1059821</v>
+        <v>0.1211224</v>
       </c>
       <c r="N9">
-        <v>2.968462344444444</v>
+        <v>2.953322044444444</v>
       </c>
       <c r="O9">
-        <v>0.5936924688888888</v>
+        <v>0.5906644088888888</v>
       </c>
       <c r="P9">
-        <v>2.374769875555555</v>
+        <v>2.362657635555555</v>
       </c>
       <c r="Q9">
-        <v>3.344769875555555</v>
+        <v>3.332657635555555</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1113098385481394</v>
+        <v>0.1118875776657701</v>
       </c>
       <c r="T9">
-        <v>0.7173595830078527</v>
+        <v>0.7236860631472641</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>29.00909157720449</v>
+        <v>25.38295513005393</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1061557714525085</v>
+        <v>0.1059765930552473</v>
       </c>
       <c r="C10">
-        <v>30.71276430764535</v>
+        <v>30.50606537223821</v>
       </c>
       <c r="D10">
-        <v>31.67076430764535</v>
+        <v>31.76506537223822</v>
       </c>
       <c r="E10">
-        <v>-10.192</v>
+        <v>-9.891</v>
       </c>
       <c r="F10">
-        <v>2.408</v>
+        <v>2.709</v>
       </c>
       <c r="G10">
         <v>1.45</v>
@@ -2107,28 +2107,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M10">
-        <v>0.1211224</v>
+        <v>0.1362627</v>
       </c>
       <c r="N10">
-        <v>2.953322044444444</v>
+        <v>2.938181744444444</v>
       </c>
       <c r="O10">
-        <v>0.5906644088888888</v>
+        <v>0.5876363488888888</v>
       </c>
       <c r="P10">
-        <v>2.362657635555555</v>
+        <v>2.350545395555555</v>
       </c>
       <c r="Q10">
-        <v>3.332657635555555</v>
+        <v>3.320545395555556</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1118875776657701</v>
+        <v>0.1124780143464256</v>
       </c>
       <c r="T10">
-        <v>0.7236860631472641</v>
+        <v>0.7301515868062229</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>25.38295513005393</v>
+        <v>22.56262678227016</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1059765930552473</v>
+        <v>0.1057974146579861</v>
       </c>
       <c r="C11">
-        <v>30.50606537223821</v>
+        <v>30.29992968488802</v>
       </c>
       <c r="D11">
-        <v>31.76506537223822</v>
+        <v>31.85992968488802</v>
       </c>
       <c r="E11">
-        <v>-9.891</v>
+        <v>-9.59</v>
       </c>
       <c r="F11">
-        <v>2.709</v>
+        <v>3.01</v>
       </c>
       <c r="G11">
         <v>1.45</v>
@@ -2189,28 +2189,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M11">
-        <v>0.1362627</v>
+        <v>0.151403</v>
       </c>
       <c r="N11">
-        <v>2.938181744444444</v>
+        <v>2.923041444444444</v>
       </c>
       <c r="O11">
-        <v>0.5876363488888888</v>
+        <v>0.5846082888888888</v>
       </c>
       <c r="P11">
-        <v>2.350545395555555</v>
+        <v>2.338433155555555</v>
       </c>
       <c r="Q11">
-        <v>3.320545395555556</v>
+        <v>3.308433155555556</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1124780143464256</v>
+        <v>0.1130815718422068</v>
       </c>
       <c r="T11">
-        <v>0.7301515868062229</v>
+        <v>0.7367607887687141</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>22.56262678227016</v>
+        <v>20.30636410404314</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1057974146579861</v>
+        <v>0.1056182362607249</v>
       </c>
       <c r="C12">
-        <v>30.29992968488802</v>
+        <v>30.09436230702203</v>
       </c>
       <c r="D12">
-        <v>31.85992968488802</v>
+        <v>31.95536230702203</v>
       </c>
       <c r="E12">
-        <v>-9.59</v>
+        <v>-9.289</v>
       </c>
       <c r="F12">
-        <v>3.01</v>
+        <v>3.311</v>
       </c>
       <c r="G12">
         <v>1.45</v>
@@ -2271,28 +2271,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M12">
-        <v>0.151403</v>
+        <v>0.1665433</v>
       </c>
       <c r="N12">
-        <v>2.923041444444444</v>
+        <v>2.907901144444444</v>
       </c>
       <c r="O12">
-        <v>0.5846082888888888</v>
+        <v>0.5815802288888888</v>
       </c>
       <c r="P12">
-        <v>2.338433155555555</v>
+        <v>2.326320915555555</v>
       </c>
       <c r="Q12">
-        <v>3.308433155555556</v>
+        <v>3.296320915555556</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1130815718422068</v>
+        <v>0.1136986924277808</v>
       </c>
       <c r="T12">
-        <v>0.7367607887687143</v>
+        <v>0.743518512123621</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>20.30636410404314</v>
+        <v>18.46033100367558</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1056182362607249</v>
+        <v>0.1054390578634637</v>
       </c>
       <c r="C13">
-        <v>30.09436230702203</v>
+        <v>29.88936836089331</v>
       </c>
       <c r="D13">
-        <v>31.95536230702203</v>
+        <v>32.05136836089331</v>
       </c>
       <c r="E13">
-        <v>-9.289</v>
+        <v>-8.988</v>
       </c>
       <c r="F13">
-        <v>3.311</v>
+        <v>3.612</v>
       </c>
       <c r="G13">
         <v>1.45</v>
@@ -2353,28 +2353,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M13">
-        <v>0.1665433</v>
+        <v>0.1816836</v>
       </c>
       <c r="N13">
-        <v>2.907901144444444</v>
+        <v>2.892760844444444</v>
       </c>
       <c r="O13">
-        <v>0.5815802288888888</v>
+        <v>0.5785521688888888</v>
       </c>
       <c r="P13">
-        <v>2.326320915555555</v>
+        <v>2.314208675555555</v>
       </c>
       <c r="Q13">
-        <v>3.296320915555556</v>
+        <v>3.284208675555556</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1136986924277808</v>
+        <v>0.1143298384812088</v>
       </c>
       <c r="T13">
-        <v>0.743518512123621</v>
+        <v>0.7504298201002303</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>18.46033100367558</v>
+        <v>16.92197008670262</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1054390578634637</v>
+        <v>0.1052598794662025</v>
       </c>
       <c r="C14">
-        <v>29.88936836089331</v>
+        <v>29.68495303049726</v>
       </c>
       <c r="D14">
-        <v>32.05136836089331</v>
+        <v>32.14795303049726</v>
       </c>
       <c r="E14">
-        <v>-8.988</v>
+        <v>-8.686999999999999</v>
       </c>
       <c r="F14">
-        <v>3.612</v>
+        <v>3.913</v>
       </c>
       <c r="G14">
         <v>1.45</v>
@@ -2435,28 +2435,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M14">
-        <v>0.1816836</v>
+        <v>0.1968239</v>
       </c>
       <c r="N14">
-        <v>2.892760844444444</v>
+        <v>2.877620544444444</v>
       </c>
       <c r="O14">
-        <v>0.5785521688888888</v>
+        <v>0.5755241088888888</v>
       </c>
       <c r="P14">
-        <v>2.314208675555555</v>
+        <v>2.302096435555555</v>
       </c>
       <c r="Q14">
-        <v>3.284208675555556</v>
+        <v>3.272096435555556</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1143298384812088</v>
+        <v>0.1149754936393132</v>
       </c>
       <c r="T14">
-        <v>0.7504298201002303</v>
+        <v>0.7575000087199799</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>16.92197008670262</v>
+        <v>15.62028008003319</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1052598794662025</v>
+        <v>0.1050807010689413</v>
       </c>
       <c r="C15">
-        <v>29.68495303049726</v>
+        <v>29.48112156250456</v>
       </c>
       <c r="D15">
-        <v>32.14795303049726</v>
+        <v>32.24512156250456</v>
       </c>
       <c r="E15">
-        <v>-8.686999999999999</v>
+        <v>-8.385999999999999</v>
       </c>
       <c r="F15">
-        <v>3.913</v>
+        <v>4.214</v>
       </c>
       <c r="G15">
         <v>1.45</v>
@@ -2517,28 +2517,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M15">
-        <v>0.1968239</v>
+        <v>0.2119642</v>
       </c>
       <c r="N15">
-        <v>2.877620544444444</v>
+        <v>2.862480244444444</v>
       </c>
       <c r="O15">
-        <v>0.5755241088888888</v>
+        <v>0.5724960488888888</v>
       </c>
       <c r="P15">
-        <v>2.302096435555555</v>
+        <v>2.289984195555555</v>
       </c>
       <c r="Q15">
-        <v>3.272096435555556</v>
+        <v>3.259984195555556</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1149754936393132</v>
+        <v>0.1156361640336527</v>
       </c>
       <c r="T15">
-        <v>0.7575000087199799</v>
+        <v>0.7647346203308866</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>15.62028008003319</v>
+        <v>14.50454578860224</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1050807010689413</v>
+        <v>0.1049015226716801</v>
       </c>
       <c r="C16">
-        <v>29.48112156250456</v>
+        <v>29.2778792672114</v>
       </c>
       <c r="D16">
-        <v>32.24512156250456</v>
+        <v>32.34287926721139</v>
       </c>
       <c r="E16">
-        <v>-8.385999999999999</v>
+        <v>-8.084999999999999</v>
       </c>
       <c r="F16">
-        <v>4.214</v>
+        <v>4.515000000000001</v>
       </c>
       <c r="G16">
         <v>1.45</v>
@@ -2599,28 +2599,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M16">
-        <v>0.2119642</v>
+        <v>0.2271045</v>
       </c>
       <c r="N16">
-        <v>2.862480244444444</v>
+        <v>2.847339944444444</v>
       </c>
       <c r="O16">
-        <v>0.5724960488888888</v>
+        <v>0.5694679888888888</v>
       </c>
       <c r="P16">
-        <v>2.289984195555555</v>
+        <v>2.277871955555555</v>
       </c>
       <c r="Q16">
-        <v>3.259984195555556</v>
+        <v>3.247871955555556</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1156361640336527</v>
+        <v>0.1163123796137413</v>
       </c>
       <c r="T16">
-        <v>0.7647346203308866</v>
+        <v>0.7721394580973439</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>14.50454578860224</v>
+        <v>13.5375760693621</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1049015226716801</v>
+        <v>0.1049143442744189</v>
       </c>
       <c r="C17">
-        <v>29.2778792672114</v>
+        <v>28.96986426003365</v>
       </c>
       <c r="D17">
-        <v>32.34287926721139</v>
+        <v>32.33586426003365</v>
       </c>
       <c r="E17">
-        <v>-8.085000000000001</v>
+        <v>-7.783999999999999</v>
       </c>
       <c r="F17">
-        <v>4.515</v>
+        <v>4.816000000000001</v>
       </c>
       <c r="G17">
         <v>1.45</v>
@@ -2681,45 +2681,45 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M17">
-        <v>0.2271045</v>
+        <v>0.2494688</v>
       </c>
       <c r="N17">
-        <v>2.847339944444444</v>
+        <v>2.824975644444444</v>
       </c>
       <c r="O17">
-        <v>0.5694679888888888</v>
+        <v>0.5649951288888889</v>
       </c>
       <c r="P17">
-        <v>2.277871955555555</v>
+        <v>2.259980515555555</v>
       </c>
       <c r="Q17">
-        <v>3.247871955555556</v>
+        <v>3.229980515555555</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1163123796137413</v>
+        <v>0.1170046955647844</v>
       </c>
       <c r="T17">
-        <v>0.7721394580973439</v>
+        <v>0.7797206015249074</v>
       </c>
       <c r="U17">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V17">
         <v>0.2</v>
       </c>
       <c r="W17">
-        <v>0.04024</v>
+        <v>0.04144</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y17">
-        <v>13.5375760693621</v>
+        <v>12.32396373592387</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1049143442744189</v>
+        <v>0.1047471658771577</v>
       </c>
       <c r="C18">
-        <v>28.96986426003365</v>
+        <v>28.76057109412153</v>
       </c>
       <c r="D18">
-        <v>32.33586426003365</v>
+        <v>32.42757109412153</v>
       </c>
       <c r="E18">
-        <v>-7.783999999999999</v>
+        <v>-7.482999999999999</v>
       </c>
       <c r="F18">
-        <v>4.816000000000001</v>
+        <v>5.117000000000001</v>
       </c>
       <c r="G18">
         <v>1.45</v>
@@ -2763,28 +2763,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M18">
-        <v>0.2494688</v>
+        <v>0.2650606</v>
       </c>
       <c r="N18">
-        <v>2.824975644444444</v>
+        <v>2.809383844444444</v>
       </c>
       <c r="O18">
-        <v>0.5649951288888889</v>
+        <v>0.5618767688888888</v>
       </c>
       <c r="P18">
-        <v>2.259980515555555</v>
+        <v>2.247507075555555</v>
       </c>
       <c r="Q18">
-        <v>3.229980515555555</v>
+        <v>3.217507075555555</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1170046955647844</v>
+        <v>0.1177136938279009</v>
       </c>
       <c r="T18">
-        <v>0.7797206015249074</v>
+        <v>0.787484423107352</v>
       </c>
       <c r="U18">
         <v>0.0518</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>12.32396373592387</v>
+        <v>11.59902469263423</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1047471658771577</v>
+        <v>0.1045799874798965</v>
       </c>
       <c r="C19">
-        <v>28.76057109412153</v>
+        <v>28.55179958199664</v>
       </c>
       <c r="D19">
-        <v>32.42757109412153</v>
+        <v>32.51979958199664</v>
       </c>
       <c r="E19">
-        <v>-7.482999999999999</v>
+        <v>-7.181999999999999</v>
       </c>
       <c r="F19">
-        <v>5.117000000000001</v>
+        <v>5.418000000000001</v>
       </c>
       <c r="G19">
         <v>1.45</v>
@@ -2845,28 +2845,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M19">
-        <v>0.2650606</v>
+        <v>0.2806524</v>
       </c>
       <c r="N19">
-        <v>2.809383844444444</v>
+        <v>2.793792044444444</v>
       </c>
       <c r="O19">
-        <v>0.5618767688888888</v>
+        <v>0.5587584088888888</v>
       </c>
       <c r="P19">
-        <v>2.247507075555555</v>
+        <v>2.235033635555555</v>
       </c>
       <c r="Q19">
-        <v>3.217507075555555</v>
+        <v>3.205033635555556</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1177136938279009</v>
+        <v>0.1184399847315811</v>
       </c>
       <c r="T19">
-        <v>0.787484423107352</v>
+        <v>0.7954376061918075</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>11.59902469263423</v>
+        <v>10.95463443193233</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1045799874798965</v>
+        <v>0.1044128090826353</v>
       </c>
       <c r="C20">
-        <v>28.55179958199664</v>
+        <v>28.34355418732034</v>
       </c>
       <c r="D20">
-        <v>32.51979958199664</v>
+        <v>32.61255418732033</v>
       </c>
       <c r="E20">
-        <v>-7.181999999999999</v>
+        <v>-6.880999999999999</v>
       </c>
       <c r="F20">
-        <v>5.418</v>
+        <v>5.719</v>
       </c>
       <c r="G20">
         <v>1.45</v>
@@ -2927,28 +2927,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M20">
-        <v>0.2806524</v>
+        <v>0.2962442</v>
       </c>
       <c r="N20">
-        <v>2.793792044444444</v>
+        <v>2.778200244444444</v>
       </c>
       <c r="O20">
-        <v>0.5587584088888888</v>
+        <v>0.5556400488888888</v>
       </c>
       <c r="P20">
-        <v>2.235033635555555</v>
+        <v>2.222560195555555</v>
       </c>
       <c r="Q20">
-        <v>3.205033635555556</v>
+        <v>3.192560195555556</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1184399847315811</v>
+        <v>0.1191842087439942</v>
       </c>
       <c r="T20">
-        <v>0.7954376061918074</v>
+        <v>0.8035871641672371</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>10.95463443193233</v>
+        <v>10.37807472498852</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1044128090826353</v>
+        <v>0.1042456306853741</v>
       </c>
       <c r="C21">
-        <v>28.34355418732034</v>
+        <v>28.13583942482561</v>
       </c>
       <c r="D21">
-        <v>32.61255418732033</v>
+        <v>32.70583942482561</v>
       </c>
       <c r="E21">
-        <v>-6.880999999999999</v>
+        <v>-6.579999999999999</v>
       </c>
       <c r="F21">
-        <v>5.719</v>
+        <v>6.02</v>
       </c>
       <c r="G21">
         <v>1.45</v>
@@ -3009,28 +3009,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M21">
-        <v>0.2962442</v>
+        <v>0.311836</v>
       </c>
       <c r="N21">
-        <v>2.778200244444444</v>
+        <v>2.762608444444444</v>
       </c>
       <c r="O21">
-        <v>0.5556400488888888</v>
+        <v>0.5525216888888889</v>
       </c>
       <c r="P21">
-        <v>2.222560195555555</v>
+        <v>2.210086755555555</v>
       </c>
       <c r="Q21">
-        <v>3.192560195555556</v>
+        <v>3.180086755555556</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1191842087439942</v>
+        <v>0.1199470383567177</v>
       </c>
       <c r="T21">
-        <v>0.8035871641672371</v>
+        <v>0.8119404610920523</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>10.37807472498852</v>
+        <v>9.859170988739093</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1042456306853741</v>
+        <v>0.1043640522881129</v>
       </c>
       <c r="C22">
-        <v>28.13583942482561</v>
+        <v>27.76870537548504</v>
       </c>
       <c r="D22">
-        <v>32.70583942482561</v>
+        <v>32.63970537548504</v>
       </c>
       <c r="E22">
-        <v>-6.579999999999999</v>
+        <v>-6.278999999999999</v>
       </c>
       <c r="F22">
-        <v>6.02</v>
+        <v>6.321000000000001</v>
       </c>
       <c r="G22">
         <v>1.45</v>
@@ -3091,45 +3091,45 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M22">
-        <v>0.311836</v>
+        <v>0.3381735</v>
       </c>
       <c r="N22">
-        <v>2.762608444444444</v>
+        <v>2.736270944444444</v>
       </c>
       <c r="O22">
-        <v>0.5525216888888889</v>
+        <v>0.5472541888888889</v>
       </c>
       <c r="P22">
-        <v>2.210086755555555</v>
+        <v>2.189016755555556</v>
       </c>
       <c r="Q22">
-        <v>3.180086755555556</v>
+        <v>3.159016755555556</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1199470383567177</v>
+        <v>0.1207291801115354</v>
       </c>
       <c r="T22">
-        <v>0.8119404610920523</v>
+        <v>0.820505233888382</v>
       </c>
       <c r="U22">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V22">
         <v>0.2</v>
       </c>
       <c r="W22">
-        <v>0.04144</v>
+        <v>0.0428</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y22">
-        <v>9.859170988739093</v>
+        <v>9.091322780893369</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1043640522881129</v>
+        <v>0.1042104738908518</v>
       </c>
       <c r="C23">
-        <v>27.76870537548504</v>
+        <v>27.55352480656877</v>
       </c>
       <c r="D23">
-        <v>32.63970537548504</v>
+        <v>32.72552480656877</v>
       </c>
       <c r="E23">
-        <v>-6.279</v>
+        <v>-5.977999999999999</v>
       </c>
       <c r="F23">
-        <v>6.321</v>
+        <v>6.622000000000001</v>
       </c>
       <c r="G23">
         <v>1.45</v>
@@ -3173,28 +3173,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M23">
-        <v>0.3381735</v>
+        <v>0.354277</v>
       </c>
       <c r="N23">
-        <v>2.736270944444444</v>
+        <v>2.720167444444444</v>
       </c>
       <c r="O23">
-        <v>0.5472541888888889</v>
+        <v>0.5440334888888888</v>
       </c>
       <c r="P23">
-        <v>2.189016755555556</v>
+        <v>2.176133955555555</v>
       </c>
       <c r="Q23">
-        <v>3.159016755555556</v>
+        <v>3.146133955555555</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1207291801115354</v>
+        <v>0.1215313767831433</v>
       </c>
       <c r="T23">
-        <v>0.820505233888382</v>
+        <v>0.829289616243592</v>
       </c>
       <c r="U23">
         <v>0.0535</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>9.091322780893371</v>
+        <v>8.678080836307307</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1042104738908518</v>
+        <v>0.1040568954935906</v>
       </c>
       <c r="C24">
-        <v>27.55352480656877</v>
+        <v>27.33879671664467</v>
       </c>
       <c r="D24">
-        <v>32.72552480656877</v>
+        <v>32.81179671664466</v>
       </c>
       <c r="E24">
-        <v>-5.977999999999999</v>
+        <v>-5.676999999999999</v>
       </c>
       <c r="F24">
-        <v>6.622000000000001</v>
+        <v>6.923000000000001</v>
       </c>
       <c r="G24">
         <v>1.45</v>
@@ -3255,28 +3255,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M24">
-        <v>0.354277</v>
+        <v>0.3703805000000001</v>
       </c>
       <c r="N24">
-        <v>2.720167444444444</v>
+        <v>2.704063944444444</v>
       </c>
       <c r="O24">
-        <v>0.5440334888888888</v>
+        <v>0.5408127888888888</v>
       </c>
       <c r="P24">
-        <v>2.176133955555555</v>
+        <v>2.163251155555555</v>
       </c>
       <c r="Q24">
-        <v>3.146133955555555</v>
+        <v>3.133251155555556</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1215313767831433</v>
+        <v>0.1223544097319358</v>
       </c>
       <c r="T24">
-        <v>0.829289616243592</v>
+        <v>0.838302164374262</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>8.678080836307307</v>
+        <v>8.300772973859162</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1040568954935906</v>
+        <v>0.1039033170963294</v>
       </c>
       <c r="C25">
-        <v>27.33879671664467</v>
+        <v>27.12452469368337</v>
       </c>
       <c r="D25">
-        <v>32.81179671664466</v>
+        <v>32.89852469368337</v>
       </c>
       <c r="E25">
-        <v>-5.676999999999999</v>
+        <v>-5.375999999999999</v>
       </c>
       <c r="F25">
-        <v>6.923000000000001</v>
+        <v>7.224000000000001</v>
       </c>
       <c r="G25">
         <v>1.45</v>
@@ -3337,28 +3337,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M25">
-        <v>0.3703805000000001</v>
+        <v>0.386484</v>
       </c>
       <c r="N25">
-        <v>2.704063944444444</v>
+        <v>2.687960444444444</v>
       </c>
       <c r="O25">
-        <v>0.5408127888888888</v>
+        <v>0.5375920888888889</v>
       </c>
       <c r="P25">
-        <v>2.163251155555555</v>
+        <v>2.150368355555555</v>
       </c>
       <c r="Q25">
-        <v>3.133251155555556</v>
+        <v>3.120368355555556</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1223544097319358</v>
+        <v>0.1231991014425386</v>
       </c>
       <c r="T25">
-        <v>0.838302164374262</v>
+        <v>0.84755188482416</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>8.300772973859162</v>
+        <v>7.954907433281698</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1039033170963293</v>
+        <v>0.1037497386990681</v>
       </c>
       <c r="C26">
-        <v>27.12452469368339</v>
+        <v>26.91071236369086</v>
       </c>
       <c r="D26">
-        <v>32.89852469368338</v>
+        <v>32.98571236369086</v>
       </c>
       <c r="E26">
-        <v>-5.375999999999999</v>
+        <v>-5.074999999999999</v>
       </c>
       <c r="F26">
-        <v>7.224</v>
+        <v>7.525</v>
       </c>
       <c r="G26">
         <v>1.45</v>
@@ -3419,28 +3419,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M26">
-        <v>0.386484</v>
+        <v>0.4025875</v>
       </c>
       <c r="N26">
-        <v>2.687960444444444</v>
+        <v>2.671856944444444</v>
       </c>
       <c r="O26">
-        <v>0.5375920888888889</v>
+        <v>0.5343713888888888</v>
       </c>
       <c r="P26">
-        <v>2.150368355555555</v>
+        <v>2.137485555555555</v>
       </c>
       <c r="Q26">
-        <v>3.120368355555556</v>
+        <v>3.107485555555555</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1231991014425386</v>
+        <v>0.1240663182654242</v>
       </c>
       <c r="T26">
-        <v>0.8475518848241599</v>
+        <v>0.8570482644860552</v>
       </c>
       <c r="U26">
         <v>0.0535</v>
@@ -3457,7 +3457,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>7.9549074332817</v>
+        <v>7.63671113595043</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1037497386990681</v>
+        <v>0.1037625603018069</v>
       </c>
       <c r="C27">
-        <v>26.91071236369086</v>
+        <v>26.60241576226777</v>
       </c>
       <c r="D27">
-        <v>32.98571236369086</v>
+        <v>32.97841576226777</v>
       </c>
       <c r="E27">
-        <v>-5.074999999999999</v>
+        <v>-4.773999999999999</v>
       </c>
       <c r="F27">
-        <v>7.525</v>
+        <v>7.826000000000001</v>
       </c>
       <c r="G27">
         <v>1.45</v>
@@ -3501,45 +3501,45 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M27">
-        <v>0.4025875</v>
+        <v>0.4249518</v>
       </c>
       <c r="N27">
-        <v>2.671856944444444</v>
+        <v>2.649492644444444</v>
       </c>
       <c r="O27">
-        <v>0.5343713888888888</v>
+        <v>0.5298985288888888</v>
       </c>
       <c r="P27">
-        <v>2.137485555555555</v>
+        <v>2.119594115555555</v>
       </c>
       <c r="Q27">
-        <v>3.107485555555555</v>
+        <v>3.089594115555555</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1240663182654242</v>
+        <v>0.1249569733808202</v>
       </c>
       <c r="T27">
-        <v>0.8570482644860552</v>
+        <v>0.8668013030577316</v>
       </c>
       <c r="U27">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V27">
         <v>0.2</v>
       </c>
       <c r="W27">
-        <v>0.0428</v>
+        <v>0.04344000000000001</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y27">
-        <v>7.63671113595043</v>
+        <v>7.234807440383695</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1037625603018069</v>
+        <v>0.1036153819045458</v>
       </c>
       <c r="C28">
-        <v>26.60241576226777</v>
+        <v>26.38536764870722</v>
       </c>
       <c r="D28">
-        <v>32.97841576226777</v>
+        <v>33.06236764870722</v>
       </c>
       <c r="E28">
-        <v>-4.773999999999999</v>
+        <v>-4.472999999999999</v>
       </c>
       <c r="F28">
-        <v>7.826000000000001</v>
+        <v>8.127000000000001</v>
       </c>
       <c r="G28">
         <v>1.45</v>
@@ -3583,28 +3583,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M28">
-        <v>0.4249518</v>
+        <v>0.4412961</v>
       </c>
       <c r="N28">
-        <v>2.649492644444444</v>
+        <v>2.633148344444444</v>
       </c>
       <c r="O28">
-        <v>0.5298985288888888</v>
+        <v>0.5266296688888888</v>
       </c>
       <c r="P28">
-        <v>2.119594115555555</v>
+        <v>2.106518675555555</v>
       </c>
       <c r="Q28">
-        <v>3.089594115555555</v>
+        <v>3.076518675555555</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1249569733808202</v>
+        <v>0.1258720300062271</v>
       </c>
       <c r="T28">
-        <v>0.8668013030577316</v>
+        <v>0.8768215481656183</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>7.234807440383695</v>
+        <v>6.966851609258373</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1036153819045458</v>
+        <v>0.1034682035072846</v>
       </c>
       <c r="C29">
-        <v>26.38536764870722</v>
+        <v>26.16874805219218</v>
       </c>
       <c r="D29">
-        <v>33.06236764870722</v>
+        <v>33.14674805219218</v>
       </c>
       <c r="E29">
-        <v>-4.472999999999999</v>
+        <v>-4.171999999999999</v>
       </c>
       <c r="F29">
-        <v>8.127000000000001</v>
+        <v>8.428000000000001</v>
       </c>
       <c r="G29">
         <v>1.45</v>
@@ -3665,28 +3665,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M29">
-        <v>0.4412961</v>
+        <v>0.4576404000000001</v>
       </c>
       <c r="N29">
-        <v>2.633148344444444</v>
+        <v>2.616804044444444</v>
       </c>
       <c r="O29">
-        <v>0.5266296688888888</v>
+        <v>0.5233608088888888</v>
       </c>
       <c r="P29">
-        <v>2.106518675555555</v>
+        <v>2.093443235555555</v>
       </c>
       <c r="Q29">
-        <v>3.076518675555555</v>
+        <v>3.063443235555555</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1258720300062271</v>
+        <v>0.1268125048712286</v>
       </c>
       <c r="T29">
-        <v>0.8768215481656183</v>
+        <v>0.8871201334153905</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>6.966851609258373</v>
+        <v>6.718035480356288</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1034682035072846</v>
+        <v>0.1033210251100233</v>
       </c>
       <c r="C30">
-        <v>26.16874805219218</v>
+        <v>25.95256026204782</v>
       </c>
       <c r="D30">
-        <v>33.14674805219218</v>
+        <v>33.23156026204781</v>
       </c>
       <c r="E30">
-        <v>-4.171999999999999</v>
+        <v>-3.870999999999999</v>
       </c>
       <c r="F30">
-        <v>8.428000000000001</v>
+        <v>8.729000000000001</v>
       </c>
       <c r="G30">
         <v>1.45</v>
@@ -3747,28 +3747,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M30">
-        <v>0.4576404000000001</v>
+        <v>0.4739847</v>
       </c>
       <c r="N30">
-        <v>2.616804044444444</v>
+        <v>2.600459744444444</v>
       </c>
       <c r="O30">
-        <v>0.5233608088888888</v>
+        <v>0.5200919488888889</v>
       </c>
       <c r="P30">
-        <v>2.093443235555555</v>
+        <v>2.080367795555556</v>
       </c>
       <c r="Q30">
-        <v>3.063443235555555</v>
+        <v>3.050367795555556</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1268125048712286</v>
+        <v>0.1277794719859484</v>
       </c>
       <c r="T30">
-        <v>0.8871201334153905</v>
+        <v>0.8977088196581142</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>6.718035480356288</v>
+        <v>6.486379084481934</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1033210251100233</v>
+        <v>0.1031738467127622</v>
       </c>
       <c r="C31">
-        <v>25.95256026204782</v>
+        <v>25.73680760135107</v>
       </c>
       <c r="D31">
-        <v>33.23156026204781</v>
+        <v>33.31680760135107</v>
       </c>
       <c r="E31">
-        <v>-3.871</v>
+        <v>-3.57</v>
       </c>
       <c r="F31">
-        <v>8.728999999999999</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="G31">
         <v>1.45</v>
@@ -3829,28 +3829,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M31">
-        <v>0.4739847</v>
+        <v>0.490329</v>
       </c>
       <c r="N31">
-        <v>2.600459744444444</v>
+        <v>2.584115444444444</v>
       </c>
       <c r="O31">
-        <v>0.5200919488888889</v>
+        <v>0.5168230888888888</v>
       </c>
       <c r="P31">
-        <v>2.080367795555556</v>
+        <v>2.067292355555555</v>
       </c>
       <c r="Q31">
-        <v>3.050367795555556</v>
+        <v>3.037292355555556</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1277794719859484</v>
+        <v>0.1287740667325174</v>
       </c>
       <c r="T31">
-        <v>0.8977088196581142</v>
+        <v>0.9086000397934872</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>6.486379084481935</v>
+        <v>6.270166448332536</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1031738467127622</v>
+        <v>0.103274668315501</v>
       </c>
       <c r="C32">
-        <v>25.73680760135107</v>
+        <v>25.37736352435234</v>
       </c>
       <c r="D32">
-        <v>33.31680760135107</v>
+        <v>33.25836352435234</v>
       </c>
       <c r="E32">
-        <v>-3.57</v>
+        <v>-3.269</v>
       </c>
       <c r="F32">
-        <v>9.029999999999999</v>
+        <v>9.331</v>
       </c>
       <c r="G32">
         <v>1.45</v>
@@ -3911,45 +3911,45 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M32">
-        <v>0.490329</v>
+        <v>0.5160043</v>
       </c>
       <c r="N32">
-        <v>2.584115444444444</v>
+        <v>2.558440144444444</v>
       </c>
       <c r="O32">
-        <v>0.5168230888888888</v>
+        <v>0.5116880288888889</v>
       </c>
       <c r="P32">
-        <v>2.067292355555555</v>
+        <v>2.046752115555555</v>
       </c>
       <c r="Q32">
-        <v>3.037292355555556</v>
+        <v>3.016752115555555</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1287740667325174</v>
+        <v>0.1297974903123202</v>
       </c>
       <c r="T32">
-        <v>0.9086000397934872</v>
+        <v>0.9198069474690158</v>
       </c>
       <c r="U32">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V32">
         <v>0.2</v>
       </c>
       <c r="W32">
-        <v>0.04344000000000001</v>
+        <v>0.04424</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y32">
-        <v>6.270166448332536</v>
+        <v>5.958176016061192</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.103274668315501</v>
+        <v>0.1031354899182398</v>
       </c>
       <c r="C33">
-        <v>25.37736352435234</v>
+        <v>25.15709616895782</v>
       </c>
       <c r="D33">
-        <v>33.25836352435234</v>
+        <v>33.33909616895782</v>
       </c>
       <c r="E33">
-        <v>-3.269</v>
+        <v>-2.967999999999998</v>
       </c>
       <c r="F33">
-        <v>9.331</v>
+        <v>9.632000000000001</v>
       </c>
       <c r="G33">
         <v>1.45</v>
@@ -3993,28 +3993,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M33">
-        <v>0.5160043</v>
+        <v>0.5326496000000001</v>
       </c>
       <c r="N33">
-        <v>2.558440144444444</v>
+        <v>2.541794844444444</v>
       </c>
       <c r="O33">
-        <v>0.5116880288888889</v>
+        <v>0.5083589688888889</v>
       </c>
       <c r="P33">
-        <v>2.046752115555555</v>
+        <v>2.033435875555555</v>
       </c>
       <c r="Q33">
-        <v>3.016752115555555</v>
+        <v>3.003435875555555</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1297974903123202</v>
+        <v>0.1308510145856467</v>
       </c>
       <c r="T33">
-        <v>0.9198069474690158</v>
+        <v>0.9313434700761777</v>
       </c>
       <c r="U33">
         <v>0.0553</v>
@@ -4031,7 +4031,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>5.958176016061192</v>
+        <v>5.771983015559279</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1031354899182398</v>
+        <v>0.1029963115209786</v>
       </c>
       <c r="C34">
-        <v>25.15709616895782</v>
+        <v>24.93722171442642</v>
       </c>
       <c r="D34">
-        <v>33.33909616895782</v>
+        <v>33.42022171442642</v>
       </c>
       <c r="E34">
-        <v>-2.967999999999998</v>
+        <v>-2.666999999999998</v>
       </c>
       <c r="F34">
-        <v>9.632000000000001</v>
+        <v>9.933000000000002</v>
       </c>
       <c r="G34">
         <v>1.45</v>
@@ -4075,28 +4075,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M34">
-        <v>0.5326496000000001</v>
+        <v>0.5492949000000001</v>
       </c>
       <c r="N34">
-        <v>2.541794844444444</v>
+        <v>2.525149544444444</v>
       </c>
       <c r="O34">
-        <v>0.5083589688888889</v>
+        <v>0.5050299088888889</v>
       </c>
       <c r="P34">
-        <v>2.033435875555555</v>
+        <v>2.020119635555555</v>
       </c>
       <c r="Q34">
-        <v>3.003435875555555</v>
+        <v>2.990119635555555</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1308510145856467</v>
+        <v>0.1319359873447442</v>
       </c>
       <c r="T34">
-        <v>0.9313434700761777</v>
+        <v>0.9432243664925086</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>5.771983015559279</v>
+        <v>5.59707443933021</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1029963115209786</v>
+        <v>0.1028571331237174</v>
       </c>
       <c r="C35">
-        <v>24.93722171442642</v>
+        <v>24.71774303594538</v>
       </c>
       <c r="D35">
-        <v>33.42022171442642</v>
+        <v>33.50174303594537</v>
       </c>
       <c r="E35">
-        <v>-2.666999999999998</v>
+        <v>-2.365999999999998</v>
       </c>
       <c r="F35">
-        <v>9.933000000000002</v>
+        <v>10.234</v>
       </c>
       <c r="G35">
         <v>1.45</v>
@@ -4157,28 +4157,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M35">
-        <v>0.5492949000000001</v>
+        <v>0.5659402000000001</v>
       </c>
       <c r="N35">
-        <v>2.525149544444444</v>
+        <v>2.508504244444444</v>
       </c>
       <c r="O35">
-        <v>0.5050299088888889</v>
+        <v>0.5017008488888889</v>
       </c>
       <c r="P35">
-        <v>2.020119635555555</v>
+        <v>2.006803395555555</v>
       </c>
       <c r="Q35">
-        <v>2.990119635555555</v>
+        <v>2.976803395555555</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1319359873447442</v>
+        <v>0.1330538380662385</v>
       </c>
       <c r="T35">
-        <v>0.9432243664925086</v>
+        <v>0.9554652900729708</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>5.59707443933021</v>
+        <v>5.432454602879321</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1028571331237174</v>
+        <v>0.1027179547264562</v>
       </c>
       <c r="C36">
-        <v>24.71774303594538</v>
+        <v>24.49866303682396</v>
       </c>
       <c r="D36">
-        <v>33.50174303594537</v>
+        <v>33.58366303682396</v>
       </c>
       <c r="E36">
-        <v>-2.365999999999998</v>
+        <v>-2.064999999999998</v>
       </c>
       <c r="F36">
-        <v>10.234</v>
+        <v>10.535</v>
       </c>
       <c r="G36">
         <v>1.45</v>
@@ -4239,28 +4239,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M36">
-        <v>0.5659402000000001</v>
+        <v>0.5825855000000001</v>
       </c>
       <c r="N36">
-        <v>2.508504244444444</v>
+        <v>2.491858944444444</v>
       </c>
       <c r="O36">
-        <v>0.5017008488888889</v>
+        <v>0.4983717888888888</v>
       </c>
       <c r="P36">
-        <v>2.006803395555555</v>
+        <v>1.993487155555555</v>
       </c>
       <c r="Q36">
-        <v>2.976803395555555</v>
+        <v>2.963487155555556</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1330538380662385</v>
+        <v>0.134206084194548</v>
       </c>
       <c r="T36">
-        <v>0.9554652900729708</v>
+        <v>0.9680828574559086</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>5.432454602879321</v>
+        <v>5.277241614225627</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1027179547264562</v>
+        <v>0.102578776329195</v>
       </c>
       <c r="C37">
-        <v>24.49866303682396</v>
+        <v>24.27998464883838</v>
       </c>
       <c r="D37">
-        <v>33.58366303682396</v>
+        <v>33.66598464883838</v>
       </c>
       <c r="E37">
-        <v>-2.064999999999998</v>
+        <v>-1.763999999999998</v>
       </c>
       <c r="F37">
-        <v>10.535</v>
+        <v>10.836</v>
       </c>
       <c r="G37">
         <v>1.45</v>
@@ -4321,28 +4321,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M37">
-        <v>0.5825855000000001</v>
+        <v>0.5992308000000002</v>
       </c>
       <c r="N37">
-        <v>2.491858944444444</v>
+        <v>2.475213644444444</v>
       </c>
       <c r="O37">
-        <v>0.4983717888888888</v>
+        <v>0.4950427288888888</v>
       </c>
       <c r="P37">
-        <v>1.993487155555555</v>
+        <v>1.980170915555555</v>
       </c>
       <c r="Q37">
-        <v>2.963487155555556</v>
+        <v>2.950170915555555</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.134206084194548</v>
+        <v>0.1353943380143672</v>
       </c>
       <c r="T37">
-        <v>0.9680828574559086</v>
+        <v>0.9810947238195634</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>5.277241614225627</v>
+        <v>5.130651569386025</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.102578776329195</v>
+        <v>0.1024395979319338</v>
       </c>
       <c r="C38">
-        <v>24.27998464883839</v>
+        <v>24.06171083258135</v>
       </c>
       <c r="D38">
-        <v>33.66598464883838</v>
+        <v>33.74871083258135</v>
       </c>
       <c r="E38">
-        <v>-1.763999999999999</v>
+        <v>-1.462999999999999</v>
       </c>
       <c r="F38">
-        <v>10.836</v>
+        <v>11.137</v>
       </c>
       <c r="G38">
         <v>1.45</v>
@@ -4403,28 +4403,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M38">
-        <v>0.5992308000000001</v>
+        <v>0.6158761</v>
       </c>
       <c r="N38">
-        <v>2.475213644444444</v>
+        <v>2.458568344444444</v>
       </c>
       <c r="O38">
-        <v>0.4950427288888888</v>
+        <v>0.4917136688888888</v>
       </c>
       <c r="P38">
-        <v>1.980170915555555</v>
+        <v>1.966854675555555</v>
       </c>
       <c r="Q38">
-        <v>2.950170915555556</v>
+        <v>2.936854675555556</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1353943380143672</v>
+        <v>0.1366203141776727</v>
       </c>
       <c r="T38">
-        <v>0.9810947238195633</v>
+        <v>0.9945196653058738</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>5.130651569386026</v>
+        <v>4.991985310753972</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1024395979319338</v>
+        <v>0.1023004195346726</v>
       </c>
       <c r="C39">
-        <v>24.06171083258135</v>
+        <v>23.84384457781714</v>
       </c>
       <c r="D39">
-        <v>33.74871083258135</v>
+        <v>33.83184457781714</v>
       </c>
       <c r="E39">
-        <v>-1.462999999999999</v>
+        <v>-1.161999999999999</v>
       </c>
       <c r="F39">
-        <v>11.137</v>
+        <v>11.438</v>
       </c>
       <c r="G39">
         <v>1.45</v>
@@ -4485,28 +4485,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M39">
-        <v>0.6158761</v>
+        <v>0.6325214</v>
       </c>
       <c r="N39">
-        <v>2.458568344444444</v>
+        <v>2.441923044444444</v>
       </c>
       <c r="O39">
-        <v>0.4917136688888888</v>
+        <v>0.4883846088888888</v>
       </c>
       <c r="P39">
-        <v>1.966854675555555</v>
+        <v>1.953538435555555</v>
       </c>
       <c r="Q39">
-        <v>2.936854675555556</v>
+        <v>2.923538435555556</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1366203141776727</v>
+        <v>0.1378858379591494</v>
       </c>
       <c r="T39">
-        <v>0.9945196653058738</v>
+        <v>1.008377669420775</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>4.991985310753972</v>
+        <v>4.860617276260446</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1023004195346726</v>
+        <v>0.1021612411374114</v>
       </c>
       <c r="C40">
-        <v>23.84384457781714</v>
+        <v>23.62638890384166</v>
       </c>
       <c r="D40">
-        <v>33.83184457781714</v>
+        <v>33.91538890384166</v>
       </c>
       <c r="E40">
-        <v>-1.161999999999999</v>
+        <v>-0.8609999999999989</v>
       </c>
       <c r="F40">
-        <v>11.438</v>
+        <v>11.739</v>
       </c>
       <c r="G40">
         <v>1.45</v>
@@ -4567,28 +4567,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M40">
-        <v>0.6325214</v>
+        <v>0.6491667000000001</v>
       </c>
       <c r="N40">
-        <v>2.441923044444444</v>
+        <v>2.425277744444444</v>
       </c>
       <c r="O40">
-        <v>0.4883846088888888</v>
+        <v>0.4850555488888889</v>
       </c>
       <c r="P40">
-        <v>1.953538435555555</v>
+        <v>1.940222195555555</v>
       </c>
       <c r="Q40">
-        <v>2.923538435555556</v>
+        <v>2.910222195555556</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1378858379591494</v>
+        <v>0.1391928543236252</v>
       </c>
       <c r="T40">
-        <v>1.008377669420775</v>
+        <v>1.022690034326328</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>4.860617276260446</v>
+        <v>4.735986064048639</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1021612411374114</v>
+        <v>0.1020220627401502</v>
       </c>
       <c r="C41">
-        <v>23.62638890384166</v>
+        <v>23.40934685984806</v>
       </c>
       <c r="D41">
-        <v>33.91538890384166</v>
+        <v>33.99934685984805</v>
       </c>
       <c r="E41">
-        <v>-0.8609999999999989</v>
+        <v>-0.5599999999999987</v>
       </c>
       <c r="F41">
-        <v>11.739</v>
+        <v>12.04</v>
       </c>
       <c r="G41">
         <v>1.45</v>
@@ -4649,28 +4649,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M41">
-        <v>0.6491667000000001</v>
+        <v>0.6658120000000001</v>
       </c>
       <c r="N41">
-        <v>2.425277744444444</v>
+        <v>2.408632444444444</v>
       </c>
       <c r="O41">
-        <v>0.4850555488888889</v>
+        <v>0.4817264888888888</v>
       </c>
       <c r="P41">
-        <v>1.940222195555555</v>
+        <v>1.926905955555555</v>
       </c>
       <c r="Q41">
-        <v>2.910222195555556</v>
+        <v>2.896905955555555</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1391928543236252</v>
+        <v>0.1405434379002504</v>
       </c>
       <c r="T41">
-        <v>1.022690034326328</v>
+        <v>1.037479478062067</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -4687,7 +4687,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>4.735986064048639</v>
+        <v>4.617586412447423</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1020220627401502</v>
+        <v>0.101882884342889</v>
       </c>
       <c r="C42">
-        <v>23.40934685984806</v>
+        <v>23.19272152529769</v>
       </c>
       <c r="D42">
-        <v>33.99934685984805</v>
+        <v>34.08372152529768</v>
       </c>
       <c r="E42">
-        <v>-0.5599999999999987</v>
+        <v>-0.2589999999999986</v>
       </c>
       <c r="F42">
-        <v>12.04</v>
+        <v>12.341</v>
       </c>
       <c r="G42">
         <v>1.45</v>
@@ -4731,28 +4731,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M42">
-        <v>0.6658120000000001</v>
+        <v>0.6824573</v>
       </c>
       <c r="N42">
-        <v>2.408632444444444</v>
+        <v>2.391987144444444</v>
       </c>
       <c r="O42">
-        <v>0.4817264888888888</v>
+        <v>0.4783974288888889</v>
       </c>
       <c r="P42">
-        <v>1.926905955555555</v>
+        <v>1.913589715555555</v>
       </c>
       <c r="Q42">
-        <v>2.896905955555555</v>
+        <v>2.883589715555556</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1405434379002504</v>
+        <v>0.1419398039709983</v>
       </c>
       <c r="T42">
-        <v>1.037479478062067</v>
+        <v>1.052770258873593</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>4.617586412447423</v>
+        <v>4.504962353607242</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.101882884342889</v>
+        <v>0.1025837059456278</v>
       </c>
       <c r="C43">
-        <v>23.19272152529769</v>
+        <v>22.47106197254615</v>
       </c>
       <c r="D43">
-        <v>34.08372152529768</v>
+        <v>33.66306197254615</v>
       </c>
       <c r="E43">
-        <v>-0.2589999999999986</v>
+        <v>0.04200000000000159</v>
       </c>
       <c r="F43">
-        <v>12.341</v>
+        <v>12.642</v>
       </c>
       <c r="G43">
         <v>1.45</v>
@@ -4813,45 +4813,45 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M43">
-        <v>0.6824573</v>
+        <v>0.7307076000000001</v>
       </c>
       <c r="N43">
-        <v>2.391987144444444</v>
+        <v>2.343736844444444</v>
       </c>
       <c r="O43">
-        <v>0.4783974288888889</v>
+        <v>0.4687473688888888</v>
       </c>
       <c r="P43">
-        <v>1.913589715555555</v>
+        <v>1.874989475555555</v>
       </c>
       <c r="Q43">
-        <v>2.883589715555556</v>
+        <v>2.844989475555555</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1419398039709983</v>
+        <v>0.1433843205959101</v>
       </c>
       <c r="T43">
-        <v>1.052770258873593</v>
+        <v>1.068588307988966</v>
       </c>
       <c r="U43">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V43">
         <v>0.2</v>
       </c>
       <c r="W43">
-        <v>0.04424</v>
+        <v>0.04624</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y43">
-        <v>4.504962353607242</v>
+        <v>4.207489349288887</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1025837059456278</v>
+        <v>0.1024645275483666</v>
       </c>
       <c r="C44">
-        <v>22.47106197254616</v>
+        <v>22.24086305298166</v>
       </c>
       <c r="D44">
-        <v>33.66306197254615</v>
+        <v>33.73386305298165</v>
       </c>
       <c r="E44">
-        <v>0.04199999999999982</v>
+        <v>0.343</v>
       </c>
       <c r="F44">
-        <v>12.642</v>
+        <v>12.943</v>
       </c>
       <c r="G44">
         <v>1.45</v>
@@ -4895,28 +4895,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M44">
-        <v>0.7307076</v>
+        <v>0.7481054</v>
       </c>
       <c r="N44">
-        <v>2.343736844444444</v>
+        <v>2.326339044444444</v>
       </c>
       <c r="O44">
-        <v>0.4687473688888888</v>
+        <v>0.4652678088888889</v>
       </c>
       <c r="P44">
-        <v>1.874989475555555</v>
+        <v>1.861071235555555</v>
       </c>
       <c r="Q44">
-        <v>2.844989475555555</v>
+        <v>2.831071235555555</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.14338432059591</v>
+        <v>0.1448795220146783</v>
       </c>
       <c r="T44">
-        <v>1.068588307988965</v>
+        <v>1.084961376371544</v>
       </c>
       <c r="U44">
         <v>0.0578</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>4.207489349288887</v>
+        <v>4.10964075977054</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1024645275483666</v>
+        <v>0.1023453491511054</v>
       </c>
       <c r="C45">
-        <v>22.24086305298166</v>
+        <v>22.01096258269435</v>
       </c>
       <c r="D45">
-        <v>33.73386305298165</v>
+        <v>33.80496258269434</v>
       </c>
       <c r="E45">
-        <v>0.343</v>
+        <v>0.6440000000000019</v>
       </c>
       <c r="F45">
-        <v>12.943</v>
+        <v>13.244</v>
       </c>
       <c r="G45">
         <v>1.45</v>
@@ -4977,28 +4977,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M45">
-        <v>0.7481054</v>
+        <v>0.7655032000000002</v>
       </c>
       <c r="N45">
-        <v>2.326339044444444</v>
+        <v>2.308941244444444</v>
       </c>
       <c r="O45">
-        <v>0.4652678088888889</v>
+        <v>0.4617882488888889</v>
       </c>
       <c r="P45">
-        <v>1.861071235555555</v>
+        <v>1.847152995555555</v>
       </c>
       <c r="Q45">
-        <v>2.831071235555555</v>
+        <v>2.817152995555555</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1448795220146783</v>
+        <v>0.1464281234841168</v>
       </c>
       <c r="T45">
-        <v>1.084961376371544</v>
+        <v>1.101919197196357</v>
       </c>
       <c r="U45">
         <v>0.0578</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>4.10964075977054</v>
+        <v>4.016239833412119</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1023453491511054</v>
+        <v>0.1034861707538442</v>
       </c>
       <c r="C46">
-        <v>22.01096258269435</v>
+        <v>21.04142398687249</v>
       </c>
       <c r="D46">
-        <v>33.80496258269434</v>
+        <v>33.13642398687249</v>
       </c>
       <c r="E46">
-        <v>0.6440000000000019</v>
+        <v>0.9450000000000021</v>
       </c>
       <c r="F46">
-        <v>13.244</v>
+        <v>13.545</v>
       </c>
       <c r="G46">
         <v>1.45</v>
@@ -5059,45 +5059,45 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M46">
-        <v>0.7655032000000002</v>
+        <v>0.8303085000000001</v>
       </c>
       <c r="N46">
-        <v>2.308941244444444</v>
+        <v>2.244135944444444</v>
       </c>
       <c r="O46">
-        <v>0.4617882488888889</v>
+        <v>0.4488271888888888</v>
       </c>
       <c r="P46">
-        <v>1.847152995555555</v>
+        <v>1.795308755555555</v>
       </c>
       <c r="Q46">
-        <v>2.817152995555555</v>
+        <v>2.765308755555555</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1464281234841168</v>
+        <v>0.1480330377342622</v>
       </c>
       <c r="T46">
-        <v>1.101919197196357</v>
+        <v>1.119493666051163</v>
       </c>
       <c r="U46">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V46">
         <v>0.2</v>
       </c>
       <c r="W46">
-        <v>0.04624</v>
+        <v>0.04904</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y46">
-        <v>4.016239833412119</v>
+        <v>3.702773661168642</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1034861707538442</v>
+        <v>0.103394992356583</v>
       </c>
       <c r="C47">
-        <v>21.04142398687249</v>
+        <v>20.79288212440265</v>
       </c>
       <c r="D47">
-        <v>33.13642398687249</v>
+        <v>33.18888212440265</v>
       </c>
       <c r="E47">
-        <v>0.9450000000000021</v>
+        <v>1.246000000000002</v>
       </c>
       <c r="F47">
-        <v>13.545</v>
+        <v>13.846</v>
       </c>
       <c r="G47">
         <v>1.45</v>
@@ -5141,28 +5141,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M47">
-        <v>0.8303085000000001</v>
+        <v>0.8487598000000001</v>
       </c>
       <c r="N47">
-        <v>2.244135944444444</v>
+        <v>2.225684644444444</v>
       </c>
       <c r="O47">
-        <v>0.4488271888888888</v>
+        <v>0.4451369288888888</v>
       </c>
       <c r="P47">
-        <v>1.795308755555555</v>
+        <v>1.780547715555555</v>
       </c>
       <c r="Q47">
-        <v>2.765308755555555</v>
+        <v>2.750547715555555</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1480330377342622</v>
+        <v>0.1496973932529315</v>
       </c>
       <c r="T47">
-        <v>1.119493666051163</v>
+        <v>1.137719041159851</v>
       </c>
       <c r="U47">
         <v>0.0613</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>3.702773661168642</v>
+        <v>3.62227858157802</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.103394992356583</v>
+        <v>0.1033038139593218</v>
       </c>
       <c r="C48">
-        <v>20.79288212440265</v>
+        <v>20.54450661781686</v>
       </c>
       <c r="D48">
-        <v>33.18888212440265</v>
+        <v>33.24150661781686</v>
       </c>
       <c r="E48">
-        <v>1.246000000000002</v>
+        <v>1.547000000000002</v>
       </c>
       <c r="F48">
-        <v>13.846</v>
+        <v>14.147</v>
       </c>
       <c r="G48">
         <v>1.45</v>
@@ -5223,28 +5223,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M48">
-        <v>0.8487598000000001</v>
+        <v>0.8672111000000001</v>
       </c>
       <c r="N48">
-        <v>2.225684644444444</v>
+        <v>2.207233344444444</v>
       </c>
       <c r="O48">
-        <v>0.4451369288888888</v>
+        <v>0.4414466688888888</v>
       </c>
       <c r="P48">
-        <v>1.780547715555555</v>
+        <v>1.765786675555555</v>
       </c>
       <c r="Q48">
-        <v>2.750547715555555</v>
+        <v>2.735786675555556</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1496973932529315</v>
+        <v>0.1514245546402299</v>
       </c>
       <c r="T48">
-        <v>1.137719041159851</v>
+        <v>1.156632166272641</v>
       </c>
       <c r="U48">
         <v>0.0613</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>3.62227858157802</v>
+        <v>3.545208824523168</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1033038139593218</v>
+        <v>0.1042878355620606</v>
       </c>
       <c r="C49">
-        <v>20.54450661781686</v>
+        <v>19.68423886059565</v>
       </c>
       <c r="D49">
-        <v>33.24150661781686</v>
+        <v>32.68223886059565</v>
       </c>
       <c r="E49">
-        <v>1.547000000000002</v>
+        <v>1.848000000000003</v>
       </c>
       <c r="F49">
-        <v>14.147</v>
+        <v>14.448</v>
       </c>
       <c r="G49">
         <v>1.45</v>
@@ -5305,45 +5305,45 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M49">
-        <v>0.8672111000000001</v>
+        <v>0.9261168000000002</v>
       </c>
       <c r="N49">
-        <v>2.207233344444444</v>
+        <v>2.148327644444444</v>
       </c>
       <c r="O49">
-        <v>0.4414466688888888</v>
+        <v>0.4296655288888888</v>
       </c>
       <c r="P49">
-        <v>1.765786675555555</v>
+        <v>1.718662115555555</v>
       </c>
       <c r="Q49">
-        <v>2.735786675555556</v>
+        <v>2.688662115555555</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1514245546402299</v>
+        <v>0.1532181453116551</v>
       </c>
       <c r="T49">
-        <v>1.156632166272641</v>
+        <v>1.176272719274384</v>
       </c>
       <c r="U49">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V49">
         <v>0.2</v>
       </c>
       <c r="W49">
-        <v>0.04904</v>
+        <v>0.05128000000000001</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y49">
-        <v>3.545208824523168</v>
+        <v>3.319715660534873</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1042878355620606</v>
+        <v>0.1042190571647994</v>
       </c>
       <c r="C50">
-        <v>19.68423886059565</v>
+        <v>19.42171657860123</v>
       </c>
       <c r="D50">
-        <v>32.68223886059565</v>
+        <v>32.72071657860123</v>
       </c>
       <c r="E50">
-        <v>1.848000000000001</v>
+        <v>2.149000000000001</v>
       </c>
       <c r="F50">
-        <v>14.448</v>
+        <v>14.749</v>
       </c>
       <c r="G50">
         <v>1.45</v>
@@ -5387,28 +5387,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M50">
-        <v>0.9261168000000001</v>
+        <v>0.9454109000000001</v>
       </c>
       <c r="N50">
-        <v>2.148327644444444</v>
+        <v>2.129033544444444</v>
       </c>
       <c r="O50">
-        <v>0.4296655288888889</v>
+        <v>0.4258067088888888</v>
       </c>
       <c r="P50">
-        <v>1.718662115555555</v>
+        <v>1.703226835555555</v>
       </c>
       <c r="Q50">
-        <v>2.688662115555555</v>
+        <v>2.673226835555555</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1532181453116551</v>
+        <v>0.1550820728721558</v>
       </c>
       <c r="T50">
-        <v>1.176272719274384</v>
+        <v>1.196683490040901</v>
       </c>
       <c r="U50">
         <v>0.0641</v>
@@ -5425,7 +5425,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>3.319715660534874</v>
+        <v>3.251966361340285</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1042190571647994</v>
+        <v>0.1041502787675382</v>
       </c>
       <c r="C51">
-        <v>19.42171657860123</v>
+        <v>19.15928500519745</v>
       </c>
       <c r="D51">
-        <v>32.72071657860123</v>
+        <v>32.75928500519745</v>
       </c>
       <c r="E51">
-        <v>2.149000000000001</v>
+        <v>2.450000000000001</v>
       </c>
       <c r="F51">
-        <v>14.749</v>
+        <v>15.05</v>
       </c>
       <c r="G51">
         <v>1.45</v>
@@ -5469,28 +5469,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M51">
-        <v>0.9454109000000001</v>
+        <v>0.9647050000000001</v>
       </c>
       <c r="N51">
-        <v>2.129033544444444</v>
+        <v>2.109739444444444</v>
       </c>
       <c r="O51">
-        <v>0.4258067088888888</v>
+        <v>0.4219478888888888</v>
       </c>
       <c r="P51">
-        <v>1.703226835555555</v>
+        <v>1.687791555555555</v>
       </c>
       <c r="Q51">
-        <v>2.673226835555555</v>
+        <v>2.657791555555556</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1550820728721558</v>
+        <v>0.1570205575350765</v>
       </c>
       <c r="T51">
-        <v>1.196683490040901</v>
+        <v>1.217910691638079</v>
       </c>
       <c r="U51">
         <v>0.0641</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>3.251966361340285</v>
+        <v>3.186927034113479</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1041502787675382</v>
+        <v>0.1040815003702771</v>
       </c>
       <c r="C52">
-        <v>19.15928500519745</v>
+        <v>18.89694446152176</v>
       </c>
       <c r="D52">
-        <v>32.75928500519745</v>
+        <v>32.79794446152175</v>
       </c>
       <c r="E52">
-        <v>2.450000000000001</v>
+        <v>2.751000000000001</v>
       </c>
       <c r="F52">
-        <v>15.05</v>
+        <v>15.351</v>
       </c>
       <c r="G52">
         <v>1.45</v>
@@ -5551,28 +5551,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M52">
-        <v>0.9647050000000001</v>
+        <v>0.9839991000000001</v>
       </c>
       <c r="N52">
-        <v>2.109739444444444</v>
+        <v>2.090445344444444</v>
       </c>
       <c r="O52">
-        <v>0.4219478888888888</v>
+        <v>0.4180890688888888</v>
       </c>
       <c r="P52">
-        <v>1.687791555555555</v>
+        <v>1.672356275555555</v>
       </c>
       <c r="Q52">
-        <v>2.657791555555556</v>
+        <v>2.642356275555556</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1570205575350765</v>
+        <v>0.1590381640209736</v>
       </c>
       <c r="T52">
-        <v>1.217910691638079</v>
+        <v>1.240004309626978</v>
       </c>
       <c r="U52">
         <v>0.0641</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>3.186927034113479</v>
+        <v>3.124438268738705</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1040815003702771</v>
+        <v>0.1040127219730159</v>
       </c>
       <c r="C53">
-        <v>18.89694446152176</v>
+        <v>18.63469527022936</v>
       </c>
       <c r="D53">
-        <v>32.79794446152175</v>
+        <v>32.83669527022936</v>
       </c>
       <c r="E53">
-        <v>2.751000000000001</v>
+        <v>3.052000000000001</v>
       </c>
       <c r="F53">
-        <v>15.351</v>
+        <v>15.652</v>
       </c>
       <c r="G53">
         <v>1.45</v>
@@ -5633,28 +5633,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M53">
-        <v>0.9839991000000001</v>
+        <v>1.0032932</v>
       </c>
       <c r="N53">
-        <v>2.090445344444444</v>
+        <v>2.071151244444444</v>
       </c>
       <c r="O53">
-        <v>0.4180890688888888</v>
+        <v>0.4142302488888888</v>
       </c>
       <c r="P53">
-        <v>1.672356275555555</v>
+        <v>1.656920995555555</v>
       </c>
       <c r="Q53">
-        <v>2.642356275555556</v>
+        <v>2.626920995555555</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1590381640209736</v>
+        <v>0.161139837443783</v>
       </c>
       <c r="T53">
-        <v>1.240004309626978</v>
+        <v>1.263018495032082</v>
       </c>
       <c r="U53">
         <v>0.0641</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>3.124438268738705</v>
+        <v>3.064352917416806</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1040127219730159</v>
+        <v>0.1039439435757547</v>
       </c>
       <c r="C54">
-        <v>18.63469527022936</v>
+        <v>18.37253775550211</v>
       </c>
       <c r="D54">
-        <v>32.83669527022936</v>
+        <v>32.87553775550211</v>
       </c>
       <c r="E54">
-        <v>3.052000000000001</v>
+        <v>3.353000000000002</v>
       </c>
       <c r="F54">
-        <v>15.652</v>
+        <v>15.953</v>
       </c>
       <c r="G54">
         <v>1.45</v>
@@ -5715,28 +5715,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M54">
-        <v>1.0032932</v>
+        <v>1.0225873</v>
       </c>
       <c r="N54">
-        <v>2.071151244444444</v>
+        <v>2.051857144444444</v>
       </c>
       <c r="O54">
-        <v>0.4142302488888888</v>
+        <v>0.4103714288888888</v>
       </c>
       <c r="P54">
-        <v>1.656920995555555</v>
+        <v>1.641485715555555</v>
       </c>
       <c r="Q54">
-        <v>2.626920995555555</v>
+        <v>2.611485715555555</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.161139837443783</v>
+        <v>0.1633309437782014</v>
       </c>
       <c r="T54">
-        <v>1.263018495032082</v>
+        <v>1.2870120074757</v>
       </c>
       <c r="U54">
         <v>0.0641</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>3.064352917416806</v>
+        <v>3.006534937842905</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1039439435757547</v>
+        <v>0.1072447651784935</v>
       </c>
       <c r="C55">
-        <v>18.37253775550211</v>
+        <v>16.30545914962278</v>
       </c>
       <c r="D55">
-        <v>32.87553775550211</v>
+        <v>31.10945914962278</v>
       </c>
       <c r="E55">
-        <v>3.353000000000002</v>
+        <v>3.654000000000002</v>
       </c>
       <c r="F55">
-        <v>15.953</v>
+        <v>16.254</v>
       </c>
       <c r="G55">
         <v>1.45</v>
@@ -5797,45 +5797,45 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M55">
-        <v>1.0225873</v>
+        <v>1.1686626</v>
       </c>
       <c r="N55">
-        <v>2.051857144444444</v>
+        <v>1.905781844444444</v>
       </c>
       <c r="O55">
-        <v>0.4103714288888888</v>
+        <v>0.3811563688888888</v>
       </c>
       <c r="P55">
-        <v>1.641485715555555</v>
+        <v>1.524625475555555</v>
       </c>
       <c r="Q55">
-        <v>2.611485715555555</v>
+        <v>2.494625475555555</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1633309437782014</v>
+        <v>0.1656173156054206</v>
       </c>
       <c r="T55">
-        <v>1.2870120074757</v>
+        <v>1.31204871611252</v>
       </c>
       <c r="U55">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V55">
         <v>0.2</v>
       </c>
       <c r="W55">
-        <v>0.05128000000000001</v>
+        <v>0.05752000000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y55">
-        <v>3.006534937842905</v>
+        <v>2.63073742964346</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1072447651784935</v>
+        <v>0.1072383867812323</v>
       </c>
       <c r="C56">
-        <v>16.30545914962278</v>
+        <v>16.00768886478024</v>
       </c>
       <c r="D56">
-        <v>31.10945914962278</v>
+        <v>31.11268886478024</v>
       </c>
       <c r="E56">
-        <v>3.654000000000002</v>
+        <v>3.955000000000004</v>
       </c>
       <c r="F56">
-        <v>16.254</v>
+        <v>16.555</v>
       </c>
       <c r="G56">
         <v>1.45</v>
@@ -5879,28 +5879,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M56">
-        <v>1.1686626</v>
+        <v>1.1903045</v>
       </c>
       <c r="N56">
-        <v>1.905781844444444</v>
+        <v>1.884139944444444</v>
       </c>
       <c r="O56">
-        <v>0.3811563688888888</v>
+        <v>0.3768279888888888</v>
       </c>
       <c r="P56">
-        <v>1.524625475555555</v>
+        <v>1.507311955555555</v>
       </c>
       <c r="Q56">
-        <v>2.494625475555555</v>
+        <v>2.477311955555555</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1656173156054206</v>
+        <v>0.1680053039582939</v>
       </c>
       <c r="T56">
-        <v>1.31204871611252</v>
+        <v>1.33819816735542</v>
       </c>
       <c r="U56">
         <v>0.07190000000000001</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.63073742964346</v>
+        <v>2.582905840013579</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1072383867812323</v>
+        <v>0.1072320083839711</v>
       </c>
       <c r="C57">
-        <v>16.00768886478024</v>
+        <v>15.70991925061107</v>
       </c>
       <c r="D57">
-        <v>31.11268886478024</v>
+        <v>31.11591925061107</v>
       </c>
       <c r="E57">
-        <v>3.955000000000004</v>
+        <v>4.256000000000002</v>
       </c>
       <c r="F57">
-        <v>16.555</v>
+        <v>16.856</v>
       </c>
       <c r="G57">
         <v>1.45</v>
@@ -5961,28 +5961,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M57">
-        <v>1.1903045</v>
+        <v>1.2119464</v>
       </c>
       <c r="N57">
-        <v>1.884139944444444</v>
+        <v>1.862498044444444</v>
       </c>
       <c r="O57">
-        <v>0.3768279888888888</v>
+        <v>0.3724996088888888</v>
       </c>
       <c r="P57">
-        <v>1.507311955555555</v>
+        <v>1.489998435555555</v>
       </c>
       <c r="Q57">
-        <v>2.477311955555555</v>
+        <v>2.459998435555555</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1680053039582939</v>
+        <v>0.1705018372362979</v>
       </c>
       <c r="T57">
-        <v>1.33819816735542</v>
+        <v>1.365536230018452</v>
       </c>
       <c r="U57">
         <v>0.07190000000000001</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.582905840013579</v>
+        <v>2.536782521441908</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1072320083839711</v>
+        <v>0.1090040299867099</v>
       </c>
       <c r="C58">
-        <v>15.70991925061107</v>
+        <v>14.5365368864999</v>
       </c>
       <c r="D58">
-        <v>31.11591925061107</v>
+        <v>30.24353688649991</v>
       </c>
       <c r="E58">
-        <v>4.256000000000002</v>
+        <v>4.557000000000004</v>
       </c>
       <c r="F58">
-        <v>16.856</v>
+        <v>17.157</v>
       </c>
       <c r="G58">
         <v>1.45</v>
@@ -6043,45 +6043,45 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M58">
-        <v>1.2119464</v>
+        <v>1.3005006</v>
       </c>
       <c r="N58">
-        <v>1.862498044444444</v>
+        <v>1.773943844444444</v>
       </c>
       <c r="O58">
-        <v>0.3724996088888888</v>
+        <v>0.3547887688888888</v>
       </c>
       <c r="P58">
-        <v>1.489998435555555</v>
+        <v>1.419155075555555</v>
       </c>
       <c r="Q58">
-        <v>2.459998435555555</v>
+        <v>2.389155075555555</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1705018372362979</v>
+        <v>0.1731144883411858</v>
       </c>
       <c r="T58">
-        <v>1.365536230018452</v>
+        <v>1.394145830479765</v>
       </c>
       <c r="U58">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V58">
         <v>0.2</v>
       </c>
       <c r="W58">
-        <v>0.05752000000000001</v>
+        <v>0.06064000000000001</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y58">
-        <v>2.536782521441908</v>
+        <v>2.36404692504136</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1090040299867099</v>
+        <v>0.1090288515894487</v>
       </c>
       <c r="C59">
-        <v>14.5365368864999</v>
+        <v>14.22366425179055</v>
       </c>
       <c r="D59">
-        <v>30.24353688649991</v>
+        <v>30.23166425179055</v>
       </c>
       <c r="E59">
-        <v>4.557000000000004</v>
+        <v>4.858000000000002</v>
       </c>
       <c r="F59">
-        <v>17.157</v>
+        <v>17.458</v>
       </c>
       <c r="G59">
         <v>1.45</v>
@@ -6125,28 +6125,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M59">
-        <v>1.3005006</v>
+        <v>1.3233164</v>
       </c>
       <c r="N59">
-        <v>1.773943844444444</v>
+        <v>1.751128044444444</v>
       </c>
       <c r="O59">
-        <v>0.3547887688888888</v>
+        <v>0.3502256088888888</v>
       </c>
       <c r="P59">
-        <v>1.419155075555555</v>
+        <v>1.400902435555555</v>
       </c>
       <c r="Q59">
-        <v>2.389155075555555</v>
+        <v>2.370902435555555</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1731144883411858</v>
+        <v>0.1758515514034493</v>
       </c>
       <c r="T59">
-        <v>1.394145830479765</v>
+        <v>1.424117792867807</v>
       </c>
       <c r="U59">
         <v>0.07580000000000001</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>2.36404692504136</v>
+        <v>2.323287495299267</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1090288515894487</v>
+        <v>0.1090536731921875</v>
       </c>
       <c r="C60">
-        <v>14.22366425179056</v>
+        <v>13.91080093504828</v>
       </c>
       <c r="D60">
-        <v>30.23166425179056</v>
+        <v>30.21980093504828</v>
       </c>
       <c r="E60">
-        <v>4.857999999999999</v>
+        <v>5.159000000000001</v>
       </c>
       <c r="F60">
-        <v>17.458</v>
+        <v>17.759</v>
       </c>
       <c r="G60">
         <v>1.45</v>
@@ -6207,28 +6207,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M60">
-        <v>1.3233164</v>
+        <v>1.3461322</v>
       </c>
       <c r="N60">
-        <v>1.751128044444444</v>
+        <v>1.728312244444444</v>
       </c>
       <c r="O60">
-        <v>0.3502256088888889</v>
+        <v>0.3456624488888888</v>
       </c>
       <c r="P60">
-        <v>1.400902435555555</v>
+        <v>1.382649795555555</v>
       </c>
       <c r="Q60">
-        <v>2.370902435555555</v>
+        <v>2.352649795555555</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1758515514034492</v>
+        <v>0.1787221297370427</v>
       </c>
       <c r="T60">
-        <v>1.424117792867806</v>
+        <v>1.455551802201606</v>
       </c>
       <c r="U60">
         <v>0.07580000000000001</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>2.323287495299268</v>
+        <v>2.283909741141652</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1090536731921875</v>
+        <v>0.1090784947949263</v>
       </c>
       <c r="C61">
-        <v>13.91080093504828</v>
+        <v>13.59794692530792</v>
       </c>
       <c r="D61">
-        <v>30.21980093504828</v>
+        <v>30.20794692530792</v>
       </c>
       <c r="E61">
-        <v>5.159000000000001</v>
+        <v>5.459999999999999</v>
       </c>
       <c r="F61">
-        <v>17.759</v>
+        <v>18.06</v>
       </c>
       <c r="G61">
         <v>1.45</v>
@@ -6289,28 +6289,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M61">
-        <v>1.3461322</v>
+        <v>1.368948</v>
       </c>
       <c r="N61">
-        <v>1.728312244444444</v>
+        <v>1.705496444444444</v>
       </c>
       <c r="O61">
-        <v>0.3456624488888888</v>
+        <v>0.3410992888888889</v>
       </c>
       <c r="P61">
-        <v>1.382649795555555</v>
+        <v>1.364397155555555</v>
       </c>
       <c r="Q61">
-        <v>2.352649795555555</v>
+        <v>2.334397155555555</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1787221297370427</v>
+        <v>0.1817362369873157</v>
       </c>
       <c r="T61">
-        <v>1.455551802201606</v>
+        <v>1.488557512002096</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>2.283909741141652</v>
+        <v>2.245844578789292</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1090784947949263</v>
+        <v>0.1091033163976651</v>
       </c>
       <c r="C62">
-        <v>13.59794692530792</v>
+        <v>13.28510221162145</v>
       </c>
       <c r="D62">
-        <v>30.20794692530792</v>
+        <v>30.19610221162145</v>
       </c>
       <c r="E62">
-        <v>5.459999999999999</v>
+        <v>5.761000000000001</v>
       </c>
       <c r="F62">
-        <v>18.06</v>
+        <v>18.361</v>
       </c>
       <c r="G62">
         <v>1.45</v>
@@ -6371,28 +6371,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M62">
-        <v>1.368948</v>
+        <v>1.3917638</v>
       </c>
       <c r="N62">
-        <v>1.705496444444444</v>
+        <v>1.682680644444444</v>
       </c>
       <c r="O62">
-        <v>0.3410992888888889</v>
+        <v>0.3365361288888888</v>
       </c>
       <c r="P62">
-        <v>1.364397155555555</v>
+        <v>1.346144515555555</v>
       </c>
       <c r="Q62">
-        <v>2.334397155555555</v>
+        <v>2.316144515555555</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1817362369873157</v>
+        <v>0.1849049138401669</v>
       </c>
       <c r="T62">
-        <v>1.488557512002096</v>
+        <v>1.523255822305175</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>2.245844578789292</v>
+        <v>2.209027454546844</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1091033163976651</v>
+        <v>0.1091281380004039</v>
       </c>
       <c r="C63">
-        <v>13.28510221162145</v>
+        <v>12.97226678305802</v>
       </c>
       <c r="D63">
-        <v>30.19610221162145</v>
+        <v>30.18426678305802</v>
       </c>
       <c r="E63">
-        <v>5.761000000000001</v>
+        <v>6.061999999999999</v>
       </c>
       <c r="F63">
-        <v>18.361</v>
+        <v>18.662</v>
       </c>
       <c r="G63">
         <v>1.45</v>
@@ -6453,28 +6453,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M63">
-        <v>1.3917638</v>
+        <v>1.4145796</v>
       </c>
       <c r="N63">
-        <v>1.682680644444444</v>
+        <v>1.659864844444444</v>
       </c>
       <c r="O63">
-        <v>0.3365361288888888</v>
+        <v>0.3319729688888888</v>
       </c>
       <c r="P63">
-        <v>1.346144515555555</v>
+        <v>1.327891875555555</v>
       </c>
       <c r="Q63">
-        <v>2.316144515555555</v>
+        <v>2.297891875555556</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1849049138401669</v>
+        <v>0.1882403631589576</v>
       </c>
       <c r="T63">
-        <v>1.523255822305175</v>
+        <v>1.559780359466311</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>2.209027454546844</v>
+        <v>2.173397979473509</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1091281380004039</v>
+        <v>0.1091529596031427</v>
       </c>
       <c r="C64">
-        <v>12.97226678305802</v>
+        <v>12.659440628704</v>
       </c>
       <c r="D64">
-        <v>30.18426678305802</v>
+        <v>30.172440628704</v>
       </c>
       <c r="E64">
-        <v>6.061999999999999</v>
+        <v>6.363000000000001</v>
       </c>
       <c r="F64">
-        <v>18.662</v>
+        <v>18.963</v>
       </c>
       <c r="G64">
         <v>1.45</v>
@@ -6535,28 +6535,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M64">
-        <v>1.4145796</v>
+        <v>1.4373954</v>
       </c>
       <c r="N64">
-        <v>1.659864844444444</v>
+        <v>1.637049044444444</v>
       </c>
       <c r="O64">
-        <v>0.3319729688888888</v>
+        <v>0.3274098088888888</v>
       </c>
       <c r="P64">
-        <v>1.327891875555555</v>
+        <v>1.309639235555555</v>
       </c>
       <c r="Q64">
-        <v>2.297891875555556</v>
+        <v>2.279639235555555</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1882403631589576</v>
+        <v>0.1917561070355208</v>
       </c>
       <c r="T64">
-        <v>1.559780359466311</v>
+        <v>1.598279195933455</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>2.173397979473509</v>
+        <v>2.138899598846945</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1091529596031427</v>
+        <v>0.1091777812058815</v>
       </c>
       <c r="C65">
-        <v>12.659440628704</v>
+        <v>12.34662373766276</v>
       </c>
       <c r="D65">
-        <v>30.172440628704</v>
+        <v>30.16062373766276</v>
       </c>
       <c r="E65">
-        <v>6.363000000000001</v>
+        <v>6.664000000000003</v>
       </c>
       <c r="F65">
-        <v>18.963</v>
+        <v>19.264</v>
       </c>
       <c r="G65">
         <v>1.45</v>
@@ -6617,28 +6617,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M65">
-        <v>1.4373954</v>
+        <v>1.4602112</v>
       </c>
       <c r="N65">
-        <v>1.637049044444444</v>
+        <v>1.614233244444444</v>
       </c>
       <c r="O65">
-        <v>0.3274098088888888</v>
+        <v>0.3228466488888888</v>
       </c>
       <c r="P65">
-        <v>1.309639235555555</v>
+        <v>1.291386595555555</v>
       </c>
       <c r="Q65">
-        <v>2.279639235555555</v>
+        <v>2.261386595555555</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1917561070355208</v>
+        <v>0.1954671700163375</v>
       </c>
       <c r="T65">
-        <v>1.598279195933455</v>
+        <v>1.638916856648773</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>2.138899598846945</v>
+        <v>2.105479292614961</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1091777812058815</v>
+        <v>0.1092026028086203</v>
       </c>
       <c r="C66">
-        <v>12.34662373766276</v>
+        <v>12.03381609905476</v>
       </c>
       <c r="D66">
-        <v>30.16062373766276</v>
+        <v>30.14881609905476</v>
       </c>
       <c r="E66">
-        <v>6.664000000000003</v>
+        <v>6.965000000000002</v>
       </c>
       <c r="F66">
-        <v>19.264</v>
+        <v>19.565</v>
       </c>
       <c r="G66">
         <v>1.45</v>
@@ -6699,28 +6699,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M66">
-        <v>1.4602112</v>
+        <v>1.483027</v>
       </c>
       <c r="N66">
-        <v>1.614233244444444</v>
+        <v>1.591417444444444</v>
       </c>
       <c r="O66">
-        <v>0.3228466488888888</v>
+        <v>0.3182834888888888</v>
       </c>
       <c r="P66">
-        <v>1.291386595555555</v>
+        <v>1.273133955555555</v>
       </c>
       <c r="Q66">
-        <v>2.261386595555555</v>
+        <v>2.243133955555555</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1954671700163375</v>
+        <v>0.1993902937389151</v>
       </c>
       <c r="T66">
-        <v>1.638916856648773</v>
+        <v>1.681876669404966</v>
       </c>
       <c r="U66">
         <v>0.07580000000000001</v>
@@ -6737,7 +6737,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>2.105479292614961</v>
+        <v>2.073087303497808</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1092026028086203</v>
+        <v>0.1092274244113591</v>
       </c>
       <c r="C67">
-        <v>12.03381609905476</v>
+        <v>11.72101770201749</v>
       </c>
       <c r="D67">
-        <v>30.14881609905476</v>
+        <v>30.13701770201749</v>
       </c>
       <c r="E67">
-        <v>6.965000000000002</v>
+        <v>7.266000000000004</v>
       </c>
       <c r="F67">
-        <v>19.565</v>
+        <v>19.866</v>
       </c>
       <c r="G67">
         <v>1.45</v>
@@ -6781,28 +6781,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M67">
-        <v>1.483027</v>
+        <v>1.5058428</v>
       </c>
       <c r="N67">
-        <v>1.591417444444444</v>
+        <v>1.568601644444444</v>
       </c>
       <c r="O67">
-        <v>0.3182834888888888</v>
+        <v>0.3137203288888888</v>
       </c>
       <c r="P67">
-        <v>1.273133955555555</v>
+        <v>1.254881315555555</v>
       </c>
       <c r="Q67">
-        <v>2.243133955555555</v>
+        <v>2.224881315555555</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1993902937389151</v>
+        <v>0.2035441894451739</v>
       </c>
       <c r="T67">
-        <v>1.681876669404966</v>
+        <v>1.727363529970347</v>
       </c>
       <c r="U67">
         <v>0.07580000000000001</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>2.073087303497808</v>
+        <v>2.041676889808447</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1092274244113591</v>
+        <v>0.1092522460140979</v>
       </c>
       <c r="C68">
-        <v>11.72101770201749</v>
+        <v>11.40822853570547</v>
       </c>
       <c r="D68">
-        <v>30.13701770201749</v>
+        <v>30.12522853570547</v>
       </c>
       <c r="E68">
-        <v>7.266000000000004</v>
+        <v>7.567000000000002</v>
       </c>
       <c r="F68">
-        <v>19.866</v>
+        <v>20.167</v>
       </c>
       <c r="G68">
         <v>1.45</v>
@@ -6863,28 +6863,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M68">
-        <v>1.5058428</v>
+        <v>1.5286586</v>
       </c>
       <c r="N68">
-        <v>1.568601644444444</v>
+        <v>1.545785844444444</v>
       </c>
       <c r="O68">
-        <v>0.3137203288888888</v>
+        <v>0.3091571688888888</v>
       </c>
       <c r="P68">
-        <v>1.254881315555555</v>
+        <v>1.236628675555555</v>
       </c>
       <c r="Q68">
-        <v>2.224881315555555</v>
+        <v>2.206628675555555</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2035441894451739</v>
+        <v>0.2079498364063574</v>
       </c>
       <c r="T68">
-        <v>1.727363529970347</v>
+        <v>1.775607169963933</v>
       </c>
       <c r="U68">
         <v>0.07580000000000001</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>2.041676889808447</v>
+        <v>2.011204100408321</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1092522460140979</v>
+        <v>0.1170018676168367</v>
       </c>
       <c r="C69">
-        <v>11.40822853570547</v>
+        <v>7.828394290737698</v>
       </c>
       <c r="D69">
-        <v>30.12522853570547</v>
+        <v>26.8463942907377</v>
       </c>
       <c r="E69">
-        <v>7.567000000000002</v>
+        <v>7.868000000000004</v>
       </c>
       <c r="F69">
-        <v>20.167</v>
+        <v>20.468</v>
       </c>
       <c r="G69">
         <v>1.45</v>
@@ -6945,45 +6945,45 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M69">
-        <v>1.5286586</v>
+        <v>1.84212</v>
       </c>
       <c r="N69">
-        <v>1.545785844444444</v>
+        <v>1.232324444444444</v>
       </c>
       <c r="O69">
-        <v>0.3091571688888888</v>
+        <v>0.2464648888888888</v>
       </c>
       <c r="P69">
-        <v>1.236628675555555</v>
+        <v>0.9858595555555552</v>
       </c>
       <c r="Q69">
-        <v>2.206628675555555</v>
+        <v>1.955859555555555</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.2079498364063574</v>
+        <v>0.2126308363026148</v>
       </c>
       <c r="T69">
-        <v>1.775607169963933</v>
+        <v>1.826866037457118</v>
       </c>
       <c r="U69">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V69">
         <v>0.2</v>
       </c>
       <c r="W69">
-        <v>0.06064000000000001</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y69">
-        <v>2.011204100408321</v>
+        <v>1.668970775217925</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1170018676168367</v>
+        <v>0.1171402892195755</v>
       </c>
       <c r="C70">
-        <v>7.828394290737698</v>
+        <v>7.475304217006091</v>
       </c>
       <c r="D70">
-        <v>26.8463942907377</v>
+        <v>26.79430421700609</v>
       </c>
       <c r="E70">
-        <v>7.868000000000004</v>
+        <v>8.169000000000002</v>
       </c>
       <c r="F70">
-        <v>20.468</v>
+        <v>20.769</v>
       </c>
       <c r="G70">
         <v>1.45</v>
@@ -7027,28 +7027,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M70">
-        <v>1.84212</v>
+        <v>1.86921</v>
       </c>
       <c r="N70">
-        <v>1.232324444444444</v>
+        <v>1.205234444444444</v>
       </c>
       <c r="O70">
-        <v>0.2464648888888888</v>
+        <v>0.2410468888888888</v>
       </c>
       <c r="P70">
-        <v>0.9858595555555552</v>
+        <v>0.9641875555555552</v>
       </c>
       <c r="Q70">
-        <v>1.955859555555555</v>
+        <v>1.934187555555555</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2126308363026148</v>
+        <v>0.2176138361921791</v>
       </c>
       <c r="T70">
-        <v>1.826866037457118</v>
+        <v>1.881431928659541</v>
       </c>
       <c r="U70">
         <v>0.09</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>1.668970775217925</v>
+        <v>1.64478279296839</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1171402892195755</v>
+        <v>0.1172787108223143</v>
       </c>
       <c r="C71">
-        <v>7.475304217006091</v>
+        <v>7.122415892618022</v>
       </c>
       <c r="D71">
-        <v>26.79430421700609</v>
+        <v>26.74241589261803</v>
       </c>
       <c r="E71">
-        <v>8.169000000000002</v>
+        <v>8.470000000000004</v>
       </c>
       <c r="F71">
-        <v>20.769</v>
+        <v>21.07</v>
       </c>
       <c r="G71">
         <v>1.45</v>
@@ -7109,28 +7109,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M71">
-        <v>1.86921</v>
+        <v>1.8963</v>
       </c>
       <c r="N71">
-        <v>1.205234444444444</v>
+        <v>1.178144444444444</v>
       </c>
       <c r="O71">
-        <v>0.2410468888888888</v>
+        <v>0.2356288888888888</v>
       </c>
       <c r="P71">
-        <v>0.9641875555555552</v>
+        <v>0.942515555555555</v>
       </c>
       <c r="Q71">
-        <v>1.934187555555555</v>
+        <v>1.912515555555555</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2176138361921791</v>
+        <v>0.2229290360743811</v>
       </c>
       <c r="T71">
-        <v>1.881431928659541</v>
+        <v>1.939635545942126</v>
       </c>
       <c r="U71">
         <v>0.09</v>
@@ -7147,7 +7147,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>1.64478279296839</v>
+        <v>1.621285895925984</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1172787108223143</v>
+        <v>0.1174171324250531</v>
       </c>
       <c r="C72">
-        <v>7.122415892618022</v>
+        <v>6.769728147750019</v>
       </c>
       <c r="D72">
-        <v>26.74241589261803</v>
+        <v>26.69072814775002</v>
       </c>
       <c r="E72">
-        <v>8.470000000000004</v>
+        <v>8.771000000000003</v>
       </c>
       <c r="F72">
-        <v>21.07</v>
+        <v>21.371</v>
       </c>
       <c r="G72">
         <v>1.45</v>
@@ -7191,28 +7191,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M72">
-        <v>1.8963</v>
+        <v>1.92339</v>
       </c>
       <c r="N72">
-        <v>1.178144444444444</v>
+        <v>1.151054444444444</v>
       </c>
       <c r="O72">
-        <v>0.2356288888888888</v>
+        <v>0.2302108888888888</v>
       </c>
       <c r="P72">
-        <v>0.942515555555555</v>
+        <v>0.9208435555555552</v>
       </c>
       <c r="Q72">
-        <v>1.912515555555555</v>
+        <v>1.890843555555555</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2229290360743811</v>
+        <v>0.2286108014657005</v>
       </c>
       <c r="T72">
-        <v>1.939635545942126</v>
+        <v>2.001853205795923</v>
       </c>
       <c r="U72">
         <v>0.09</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>1.621285895925984</v>
+        <v>1.598450883307308</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1174171324250531</v>
+        <v>0.1175555540277919</v>
       </c>
       <c r="C73">
-        <v>6.769728147750023</v>
+        <v>6.41723982160531</v>
       </c>
       <c r="D73">
-        <v>26.69072814775002</v>
+        <v>26.63923982160531</v>
       </c>
       <c r="E73">
-        <v>8.770999999999999</v>
+        <v>9.072000000000001</v>
       </c>
       <c r="F73">
-        <v>21.371</v>
+        <v>21.672</v>
       </c>
       <c r="G73">
         <v>1.45</v>
@@ -7273,28 +7273,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M73">
-        <v>1.92339</v>
+        <v>1.95048</v>
       </c>
       <c r="N73">
-        <v>1.151054444444444</v>
+        <v>1.123964444444444</v>
       </c>
       <c r="O73">
-        <v>0.2302108888888889</v>
+        <v>0.2247928888888888</v>
       </c>
       <c r="P73">
-        <v>0.9208435555555555</v>
+        <v>0.8991715555555553</v>
       </c>
       <c r="Q73">
-        <v>1.890843555555556</v>
+        <v>1.869171555555555</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2286108014657005</v>
+        <v>0.234698407242114</v>
       </c>
       <c r="T73">
-        <v>2.001853205795922</v>
+        <v>2.068514984210705</v>
       </c>
       <c r="U73">
         <v>0.09</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>1.598450883307309</v>
+        <v>1.576250176594707</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1175555540277919</v>
+        <v>0.1176939756305307</v>
       </c>
       <c r="C74">
-        <v>6.41723982160531</v>
+        <v>6.064949762326918</v>
       </c>
       <c r="D74">
-        <v>26.63923982160531</v>
+        <v>26.58794976232692</v>
       </c>
       <c r="E74">
-        <v>9.072000000000001</v>
+        <v>9.372999999999999</v>
       </c>
       <c r="F74">
-        <v>21.672</v>
+        <v>21.973</v>
       </c>
       <c r="G74">
         <v>1.45</v>
@@ -7355,28 +7355,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M74">
-        <v>1.95048</v>
+        <v>1.97757</v>
       </c>
       <c r="N74">
-        <v>1.123964444444444</v>
+        <v>1.096874444444444</v>
       </c>
       <c r="O74">
-        <v>0.2247928888888888</v>
+        <v>0.2193748888888889</v>
       </c>
       <c r="P74">
-        <v>0.8991715555555553</v>
+        <v>0.8774995555555554</v>
       </c>
       <c r="Q74">
-        <v>1.869171555555555</v>
+        <v>1.847499555555556</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.234698407242114</v>
+        <v>0.2412369467797434</v>
       </c>
       <c r="T74">
-        <v>2.068514984210705</v>
+        <v>2.140114672137693</v>
       </c>
       <c r="U74">
         <v>0.09</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>1.576250176594707</v>
+        <v>1.554657708422177</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1176939756305307</v>
+        <v>0.1178323972332695</v>
       </c>
       <c r="C75">
-        <v>6.064949762326918</v>
+        <v>5.712856826911732</v>
       </c>
       <c r="D75">
-        <v>26.58794976232692</v>
+        <v>26.53685682691173</v>
       </c>
       <c r="E75">
-        <v>9.372999999999999</v>
+        <v>9.674000000000001</v>
       </c>
       <c r="F75">
-        <v>21.973</v>
+        <v>22.274</v>
       </c>
       <c r="G75">
         <v>1.45</v>
@@ -7437,28 +7437,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M75">
-        <v>1.97757</v>
+        <v>2.00466</v>
       </c>
       <c r="N75">
-        <v>1.096874444444444</v>
+        <v>1.069784444444444</v>
       </c>
       <c r="O75">
-        <v>0.2193748888888889</v>
+        <v>0.2139568888888889</v>
       </c>
       <c r="P75">
-        <v>0.8774995555555554</v>
+        <v>0.8558275555555553</v>
       </c>
       <c r="Q75">
-        <v>1.847499555555556</v>
+        <v>1.825827555555556</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2412369467797434</v>
+        <v>0.2482784508971905</v>
       </c>
       <c r="T75">
-        <v>2.140114672137693</v>
+        <v>2.217222028366758</v>
       </c>
       <c r="U75">
         <v>0.09</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>1.554657708422177</v>
+        <v>1.533648820470526</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1178323972332695</v>
+        <v>0.1179708188360083</v>
       </c>
       <c r="C76">
-        <v>5.712856826911732</v>
+        <v>5.360959881125677</v>
       </c>
       <c r="D76">
-        <v>26.53685682691173</v>
+        <v>26.48595988112568</v>
       </c>
       <c r="E76">
-        <v>9.674000000000001</v>
+        <v>9.975000000000003</v>
       </c>
       <c r="F76">
-        <v>22.274</v>
+        <v>22.575</v>
       </c>
       <c r="G76">
         <v>1.45</v>
@@ -7519,28 +7519,28 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M76">
-        <v>2.00466</v>
+        <v>2.03175</v>
       </c>
       <c r="N76">
-        <v>1.069784444444444</v>
+        <v>1.042694444444444</v>
       </c>
       <c r="O76">
-        <v>0.2139568888888889</v>
+        <v>0.2085388888888888</v>
       </c>
       <c r="P76">
-        <v>0.8558275555555553</v>
+        <v>0.8341555555555551</v>
       </c>
       <c r="Q76">
-        <v>1.825827555555556</v>
+        <v>1.804155555555555</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2482784508971905</v>
+        <v>0.2558832753440334</v>
       </c>
       <c r="T76">
-        <v>2.217222028366758</v>
+        <v>2.300497973094149</v>
       </c>
       <c r="U76">
         <v>0.09</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>1.533648820470526</v>
+        <v>1.513200169530919</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1179708188360083</v>
+        <v>0.1553226158999653</v>
       </c>
       <c r="C77">
-        <v>5.360959881125677</v>
+        <v>-3.972861243485777</v>
       </c>
       <c r="D77">
-        <v>26.48595988112568</v>
+        <v>17.45313875651422</v>
       </c>
       <c r="E77">
-        <v>9.975000000000003</v>
+        <v>10.276</v>
       </c>
       <c r="F77">
-        <v>22.575</v>
+        <v>22.876</v>
       </c>
       <c r="G77">
         <v>1.45</v>
@@ -7601,45 +7601,45 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M77">
-        <v>2.03175</v>
+        <v>3.3581968</v>
       </c>
       <c r="N77">
-        <v>1.042694444444444</v>
+        <v>-0.2837523555555563</v>
       </c>
       <c r="O77">
-        <v>0.2085388888888888</v>
+        <v>-0.05675047111111127</v>
       </c>
       <c r="P77">
-        <v>0.8341555555555551</v>
+        <v>-0.2270018844444451</v>
       </c>
       <c r="Q77">
-        <v>1.804155555555555</v>
+        <v>0.7429981155555552</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2558832753440334</v>
+        <v>0.2674284091193031</v>
       </c>
       <c r="T77">
-        <v>2.300497973094149</v>
+        <v>2.426921920005747</v>
       </c>
       <c r="U77">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V77">
-        <v>0.2</v>
+        <v>0.183100909657495</v>
       </c>
       <c r="W77">
-        <v>0.07199999999999999</v>
+        <v>0.1199207864622798</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y77">
-        <v>1.513200169530919</v>
+        <v>0.9155045482874749</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1553226158999653</v>
+        <v>0.1563326158999654</v>
       </c>
       <c r="C78">
-        <v>-3.972861243485777</v>
+        <v>-4.433340597163909</v>
       </c>
       <c r="D78">
-        <v>17.45313875651422</v>
+        <v>17.2936594028361</v>
       </c>
       <c r="E78">
-        <v>10.276</v>
+        <v>10.577</v>
       </c>
       <c r="F78">
-        <v>22.876</v>
+        <v>23.177</v>
       </c>
       <c r="G78">
         <v>1.45</v>
@@ -7683,37 +7683,37 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M78">
-        <v>3.3581968</v>
+        <v>3.402383600000001</v>
       </c>
       <c r="N78">
-        <v>-0.2837523555555563</v>
+        <v>-0.3279391555555566</v>
       </c>
       <c r="O78">
-        <v>-0.05675047111111127</v>
+        <v>-0.06558783111111133</v>
       </c>
       <c r="P78">
-        <v>-0.2270018844444451</v>
+        <v>-0.2623513244444453</v>
       </c>
       <c r="Q78">
-        <v>0.7429981155555552</v>
+        <v>0.7076486755555549</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2674284091193031</v>
+        <v>0.2770644269070989</v>
       </c>
       <c r="T78">
-        <v>2.426921920005747</v>
+        <v>2.532440264353823</v>
       </c>
       <c r="U78">
         <v>0.1468</v>
       </c>
       <c r="V78">
-        <v>0.183100909657495</v>
+        <v>0.1807229757658392</v>
       </c>
       <c r="W78">
-        <v>0.1199207864622798</v>
+        <v>0.1202698671575748</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.9155045482874749</v>
+        <v>0.9036148788291959</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1563326158999654</v>
+        <v>0.1573426158999653</v>
       </c>
       <c r="C79">
-        <v>-4.433340597163909</v>
+        <v>-4.890931832324902</v>
       </c>
       <c r="D79">
-        <v>17.2936594028361</v>
+        <v>17.1370681676751</v>
       </c>
       <c r="E79">
-        <v>10.577</v>
+        <v>10.878</v>
       </c>
       <c r="F79">
-        <v>23.177</v>
+        <v>23.478</v>
       </c>
       <c r="G79">
         <v>1.45</v>
@@ -7765,37 +7765,37 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M79">
-        <v>3.402383600000001</v>
+        <v>3.446570400000001</v>
       </c>
       <c r="N79">
-        <v>-0.3279391555555566</v>
+        <v>-0.3721259555555565</v>
       </c>
       <c r="O79">
-        <v>-0.06558783111111133</v>
+        <v>-0.0744251911111113</v>
       </c>
       <c r="P79">
-        <v>-0.2623513244444453</v>
+        <v>-0.2977007644444452</v>
       </c>
       <c r="Q79">
-        <v>0.7076486755555549</v>
+        <v>0.672299235555555</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2770644269070989</v>
+        <v>0.287576446311967</v>
       </c>
       <c r="T79">
-        <v>2.532440264353823</v>
+        <v>2.647551185460815</v>
       </c>
       <c r="U79">
         <v>0.1468</v>
       </c>
       <c r="V79">
-        <v>0.1807229757658392</v>
+        <v>0.178406014538072</v>
       </c>
       <c r="W79">
-        <v>0.1202698671575748</v>
+        <v>0.120609997065811</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.9036148788291959</v>
+        <v>0.8920300726903602</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1573426158999653</v>
+        <v>0.1583526158999654</v>
       </c>
       <c r="C80">
-        <v>-4.890931832324902</v>
+        <v>-5.345712699263931</v>
       </c>
       <c r="D80">
-        <v>17.1370681676751</v>
+        <v>16.98328730073607</v>
       </c>
       <c r="E80">
-        <v>10.878</v>
+        <v>11.179</v>
       </c>
       <c r="F80">
-        <v>23.478</v>
+        <v>23.779</v>
       </c>
       <c r="G80">
         <v>1.45</v>
@@ -7847,37 +7847,37 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M80">
-        <v>3.446570400000001</v>
+        <v>3.490757200000001</v>
       </c>
       <c r="N80">
-        <v>-0.3721259555555565</v>
+        <v>-0.4163127555555568</v>
       </c>
       <c r="O80">
-        <v>-0.0744251911111113</v>
+        <v>-0.08326255111111136</v>
       </c>
       <c r="P80">
-        <v>-0.2977007644444452</v>
+        <v>-0.3330502044444454</v>
       </c>
       <c r="Q80">
-        <v>0.672299235555555</v>
+        <v>0.6369497955555548</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.287576446311967</v>
+        <v>0.2990896104220607</v>
       </c>
       <c r="T80">
-        <v>2.647551185460815</v>
+        <v>2.77362505143514</v>
       </c>
       <c r="U80">
         <v>0.1468</v>
       </c>
       <c r="V80">
-        <v>0.178406014538072</v>
+        <v>0.1761477105565774</v>
       </c>
       <c r="W80">
-        <v>0.120609997065811</v>
+        <v>0.1209415160902945</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.8920300726903602</v>
+        <v>0.8807385527828872</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1583526158999654</v>
+        <v>0.1593626158999653</v>
       </c>
       <c r="C81">
-        <v>-5.345712699263931</v>
+        <v>-5.79775818230258</v>
       </c>
       <c r="D81">
-        <v>16.98328730073607</v>
+        <v>16.83224181769742</v>
       </c>
       <c r="E81">
-        <v>11.179</v>
+        <v>11.48</v>
       </c>
       <c r="F81">
-        <v>23.779</v>
+        <v>24.08</v>
       </c>
       <c r="G81">
         <v>1.45</v>
@@ -7929,37 +7929,37 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M81">
-        <v>3.490757200000001</v>
+        <v>3.534944000000001</v>
       </c>
       <c r="N81">
-        <v>-0.4163127555555568</v>
+        <v>-0.4604995555555567</v>
       </c>
       <c r="O81">
-        <v>-0.08326255111111136</v>
+        <v>-0.09209991111111133</v>
       </c>
       <c r="P81">
-        <v>-0.3330502044444454</v>
+        <v>-0.3683996444444453</v>
       </c>
       <c r="Q81">
-        <v>0.6369497955555548</v>
+        <v>0.6016003555555549</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2990896104220607</v>
+        <v>0.3117540909431637</v>
       </c>
       <c r="T81">
-        <v>2.77362505143514</v>
+        <v>2.912306304006896</v>
       </c>
       <c r="U81">
         <v>0.1468</v>
       </c>
       <c r="V81">
-        <v>0.1761477105565774</v>
+        <v>0.1739458641746202</v>
       </c>
       <c r="W81">
-        <v>0.1209415160902945</v>
+        <v>0.1212647471391658</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.8807385527828872</v>
+        <v>0.8697293208731011</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1593626158999653</v>
+        <v>0.1603726158999653</v>
       </c>
       <c r="C82">
-        <v>-5.79775818230258</v>
+        <v>-6.247140621704318</v>
       </c>
       <c r="D82">
-        <v>16.83224181769742</v>
+        <v>16.68385937829569</v>
       </c>
       <c r="E82">
-        <v>11.48</v>
+        <v>11.781</v>
       </c>
       <c r="F82">
-        <v>24.08</v>
+        <v>24.381</v>
       </c>
       <c r="G82">
         <v>1.45</v>
@@ -8011,37 +8011,37 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M82">
-        <v>3.534944000000001</v>
+        <v>3.579130800000001</v>
       </c>
       <c r="N82">
-        <v>-0.4604995555555567</v>
+        <v>-0.504686355555557</v>
       </c>
       <c r="O82">
-        <v>-0.09209991111111133</v>
+        <v>-0.1009372711111114</v>
       </c>
       <c r="P82">
-        <v>-0.3683996444444453</v>
+        <v>-0.4037490844444456</v>
       </c>
       <c r="Q82">
-        <v>0.6016003555555549</v>
+        <v>0.5662509155555546</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3117540909431637</v>
+        <v>0.3257516746770145</v>
       </c>
       <c r="T82">
-        <v>2.912306304006896</v>
+        <v>3.065585583165155</v>
       </c>
       <c r="U82">
         <v>0.1468</v>
       </c>
       <c r="V82">
-        <v>0.1739458641746202</v>
+        <v>0.1717983843699953</v>
       </c>
       <c r="W82">
-        <v>0.1212647471391658</v>
+        <v>0.1215799971744847</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.8697293208731011</v>
+        <v>0.8589919218499763</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1603726158999653</v>
+        <v>0.1613826158999654</v>
       </c>
       <c r="C83">
-        <v>-6.247140621704318</v>
+        <v>-6.693929829197792</v>
       </c>
       <c r="D83">
-        <v>16.68385937829569</v>
+        <v>16.53807017080221</v>
       </c>
       <c r="E83">
-        <v>11.781</v>
+        <v>12.082</v>
       </c>
       <c r="F83">
-        <v>24.381</v>
+        <v>24.682</v>
       </c>
       <c r="G83">
         <v>1.45</v>
@@ -8093,37 +8093,37 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M83">
-        <v>3.579130800000001</v>
+        <v>3.6233176</v>
       </c>
       <c r="N83">
-        <v>-0.504686355555557</v>
+        <v>-0.5488731555555564</v>
       </c>
       <c r="O83">
-        <v>-0.1009372711111114</v>
+        <v>-0.1097746311111113</v>
       </c>
       <c r="P83">
-        <v>-0.4037490844444456</v>
+        <v>-0.4390985244444451</v>
       </c>
       <c r="Q83">
-        <v>0.5662509155555546</v>
+        <v>0.5309014755555551</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3257516746770145</v>
+        <v>0.3413045454924042</v>
       </c>
       <c r="T83">
-        <v>3.065585583165155</v>
+        <v>3.235895893340996</v>
       </c>
       <c r="U83">
         <v>0.1468</v>
       </c>
       <c r="V83">
-        <v>0.1717983843699953</v>
+        <v>0.1697032821215807</v>
       </c>
       <c r="W83">
-        <v>0.1215799971744847</v>
+        <v>0.121887558184552</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.8589919218499763</v>
+        <v>0.8485164106079035</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1613826158999654</v>
+        <v>0.1623926158999653</v>
       </c>
       <c r="C84">
-        <v>-6.693929829197792</v>
+        <v>-7.138193197495848</v>
       </c>
       <c r="D84">
-        <v>16.53807017080221</v>
+        <v>16.39480680250416</v>
       </c>
       <c r="E84">
-        <v>12.082</v>
+        <v>12.383</v>
       </c>
       <c r="F84">
-        <v>24.682</v>
+        <v>24.983</v>
       </c>
       <c r="G84">
         <v>1.45</v>
@@ -8175,37 +8175,37 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M84">
-        <v>3.6233176</v>
+        <v>3.667504400000001</v>
       </c>
       <c r="N84">
-        <v>-0.5488731555555564</v>
+        <v>-0.5930599555555567</v>
       </c>
       <c r="O84">
-        <v>-0.1097746311111113</v>
+        <v>-0.1186119911111113</v>
       </c>
       <c r="P84">
-        <v>-0.4390985244444451</v>
+        <v>-0.4744479644444454</v>
       </c>
       <c r="Q84">
-        <v>0.5309014755555551</v>
+        <v>0.4955520355555548</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3413045454924042</v>
+        <v>0.3586871658154868</v>
       </c>
       <c r="T84">
-        <v>3.235895893340996</v>
+        <v>3.426242710596349</v>
       </c>
       <c r="U84">
         <v>0.1468</v>
       </c>
       <c r="V84">
-        <v>0.1697032821215807</v>
+        <v>0.1676586642646942</v>
       </c>
       <c r="W84">
-        <v>0.121887558184552</v>
+        <v>0.1221877080859429</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.8485164106079035</v>
+        <v>0.8382933213234709</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1623926158999653</v>
+        <v>0.1634026158999654</v>
       </c>
       <c r="C85">
-        <v>-7.138193197495848</v>
+        <v>-7.579995804170974</v>
       </c>
       <c r="D85">
-        <v>16.39480680250416</v>
+        <v>16.25400419582903</v>
       </c>
       <c r="E85">
-        <v>12.383</v>
+        <v>12.684</v>
       </c>
       <c r="F85">
-        <v>24.983</v>
+        <v>25.284</v>
       </c>
       <c r="G85">
         <v>1.45</v>
@@ -8257,37 +8257,37 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M85">
-        <v>3.667504400000001</v>
+        <v>3.711691200000001</v>
       </c>
       <c r="N85">
-        <v>-0.5930599555555567</v>
+        <v>-0.6372467555555565</v>
       </c>
       <c r="O85">
-        <v>-0.1186119911111113</v>
+        <v>-0.1274493511111113</v>
       </c>
       <c r="P85">
-        <v>-0.4744479644444454</v>
+        <v>-0.5097974044444452</v>
       </c>
       <c r="Q85">
-        <v>0.4955520355555548</v>
+        <v>0.460202595555555</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3586871658154868</v>
+        <v>0.3782426136789548</v>
       </c>
       <c r="T85">
-        <v>3.426242710596349</v>
+        <v>3.640382880008622</v>
       </c>
       <c r="U85">
         <v>0.1468</v>
       </c>
       <c r="V85">
-        <v>0.1676586642646942</v>
+        <v>0.1656627277853526</v>
       </c>
       <c r="W85">
-        <v>0.1221877080859429</v>
+        <v>0.1224807115611102</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8295,7 +8295,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.8382933213234709</v>
+        <v>0.8283136389267629</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1634026158999654</v>
+        <v>0.1644126158999654</v>
       </c>
       <c r="C86">
-        <v>-7.57999580417097</v>
+        <v>-8.019400510223765</v>
       </c>
       <c r="D86">
-        <v>16.25400419582903</v>
+        <v>16.11559948977624</v>
       </c>
       <c r="E86">
-        <v>12.684</v>
+        <v>12.985</v>
       </c>
       <c r="F86">
-        <v>25.284</v>
+        <v>25.585</v>
       </c>
       <c r="G86">
         <v>1.45</v>
@@ -8339,37 +8339,37 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M86">
-        <v>3.7116912</v>
+        <v>3.755878</v>
       </c>
       <c r="N86">
-        <v>-0.6372467555555561</v>
+        <v>-0.6814335555555564</v>
       </c>
       <c r="O86">
-        <v>-0.1274493511111112</v>
+        <v>-0.1362867111111113</v>
       </c>
       <c r="P86">
-        <v>-0.5097974044444449</v>
+        <v>-0.5451468444444452</v>
       </c>
       <c r="Q86">
-        <v>0.4602025955555553</v>
+        <v>0.424853155555555</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3782426136789546</v>
+        <v>0.4004054545908849</v>
       </c>
       <c r="T86">
-        <v>3.64038288000862</v>
+        <v>3.883075072009194</v>
       </c>
       <c r="U86">
         <v>0.1468</v>
       </c>
       <c r="V86">
-        <v>0.1656627277853526</v>
+        <v>0.1637137545172896</v>
       </c>
       <c r="W86">
-        <v>0.1224807115611102</v>
+        <v>0.1227668208368619</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.8283136389267631</v>
+        <v>0.8185687725864481</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1644126158999654</v>
+        <v>0.1654226158999653</v>
       </c>
       <c r="C87">
-        <v>-8.019400510223765</v>
+        <v>-8.456468053657897</v>
       </c>
       <c r="D87">
-        <v>16.11559948977624</v>
+        <v>15.9795319463421</v>
       </c>
       <c r="E87">
-        <v>12.985</v>
+        <v>13.286</v>
       </c>
       <c r="F87">
-        <v>25.585</v>
+        <v>25.886</v>
       </c>
       <c r="G87">
         <v>1.45</v>
@@ -8421,37 +8421,37 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M87">
-        <v>3.755878</v>
+        <v>3.8000648</v>
       </c>
       <c r="N87">
-        <v>-0.6814335555555564</v>
+        <v>-0.7256203555555563</v>
       </c>
       <c r="O87">
-        <v>-0.1362867111111113</v>
+        <v>-0.1451240711111113</v>
       </c>
       <c r="P87">
-        <v>-0.5451468444444452</v>
+        <v>-0.580496284444445</v>
       </c>
       <c r="Q87">
-        <v>0.424853155555555</v>
+        <v>0.3895037155555552</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.4004054545908849</v>
+        <v>0.4257344156330909</v>
       </c>
       <c r="T87">
-        <v>3.883075072009194</v>
+        <v>4.160437577152708</v>
       </c>
       <c r="U87">
         <v>0.1468</v>
       </c>
       <c r="V87">
-        <v>0.1637137545172896</v>
+        <v>0.1618101062089491</v>
       </c>
       <c r="W87">
-        <v>0.1227668208368619</v>
+        <v>0.1230462764085263</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.8185687725864481</v>
+        <v>0.8090505310447453</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1654226158999653</v>
+        <v>0.2157249293654341</v>
       </c>
       <c r="C88">
-        <v>-8.456468053657897</v>
+        <v>-13.48783591667896</v>
       </c>
       <c r="D88">
-        <v>15.9795319463421</v>
+        <v>11.24916408332104</v>
       </c>
       <c r="E88">
-        <v>13.286</v>
+        <v>13.587</v>
       </c>
       <c r="F88">
-        <v>25.886</v>
+        <v>26.187</v>
       </c>
       <c r="G88">
         <v>1.45</v>
@@ -8503,45 +8503,45 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M88">
-        <v>3.8000648</v>
+        <v>5.258349600000001</v>
       </c>
       <c r="N88">
-        <v>-0.7256203555555563</v>
+        <v>-2.183905155555557</v>
       </c>
       <c r="O88">
-        <v>-0.1451240711111113</v>
+        <v>-0.4367810311111113</v>
       </c>
       <c r="P88">
-        <v>-0.580496284444445</v>
+        <v>-1.747124124444445</v>
       </c>
       <c r="Q88">
-        <v>0.3895037155555552</v>
+        <v>-0.7771241244444451</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4257344156330909</v>
+        <v>0.4727471665700115</v>
       </c>
       <c r="T88">
-        <v>4.160437577152708</v>
+        <v>4.675246469306805</v>
       </c>
       <c r="U88">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.1618101062089491</v>
+        <v>0.1169357185549034</v>
       </c>
       <c r="W88">
-        <v>0.1230462764085263</v>
+        <v>0.1773193077141754</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y88">
-        <v>0.8090505310447453</v>
+        <v>0.5846785927745168</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2157249293654341</v>
+        <v>0.2172749293654341</v>
       </c>
       <c r="C89">
-        <v>-13.48783591667896</v>
+        <v>-13.8905196111623</v>
       </c>
       <c r="D89">
-        <v>11.24916408332104</v>
+        <v>11.1474803888377</v>
       </c>
       <c r="E89">
-        <v>13.587</v>
+        <v>13.888</v>
       </c>
       <c r="F89">
-        <v>26.187</v>
+        <v>26.488</v>
       </c>
       <c r="G89">
         <v>1.45</v>
@@ -8585,37 +8585,37 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M89">
-        <v>5.258349600000001</v>
+        <v>5.318790400000001</v>
       </c>
       <c r="N89">
-        <v>-2.183905155555557</v>
+        <v>-2.244345955555557</v>
       </c>
       <c r="O89">
-        <v>-0.4367810311111113</v>
+        <v>-0.4488691911111114</v>
       </c>
       <c r="P89">
-        <v>-1.747124124444445</v>
+        <v>-1.795476764444446</v>
       </c>
       <c r="Q89">
-        <v>-0.7771241244444451</v>
+        <v>-0.8254767644444454</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.4727471665700115</v>
+        <v>0.5083260971175124</v>
       </c>
       <c r="T89">
-        <v>4.675246469306805</v>
+        <v>5.064850341749038</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.1169357185549034</v>
+        <v>0.1156069035713249</v>
       </c>
       <c r="W89">
-        <v>0.1773193077141754</v>
+        <v>0.177586133762878</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.5846785927745168</v>
+        <v>0.5780345178566246</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2172749293654341</v>
+        <v>0.2188249293654341</v>
       </c>
       <c r="C90">
-        <v>-13.8905196111623</v>
+        <v>-14.29138149040749</v>
       </c>
       <c r="D90">
-        <v>11.1474803888377</v>
+        <v>11.04761850959251</v>
       </c>
       <c r="E90">
-        <v>13.888</v>
+        <v>14.189</v>
       </c>
       <c r="F90">
-        <v>26.488</v>
+        <v>26.789</v>
       </c>
       <c r="G90">
         <v>1.45</v>
@@ -8667,37 +8667,37 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M90">
-        <v>5.318790400000001</v>
+        <v>5.3792312</v>
       </c>
       <c r="N90">
-        <v>-2.244345955555557</v>
+        <v>-2.304786755555556</v>
       </c>
       <c r="O90">
-        <v>-0.4488691911111114</v>
+        <v>-0.4609573511111113</v>
       </c>
       <c r="P90">
-        <v>-1.795476764444446</v>
+        <v>-1.843829404444445</v>
       </c>
       <c r="Q90">
-        <v>-0.8254767644444454</v>
+        <v>-0.8738294044444448</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5083260971175124</v>
+        <v>0.5503739241281954</v>
       </c>
       <c r="T90">
-        <v>5.064850341749038</v>
+        <v>5.525291281908042</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.1156069035713249</v>
+        <v>0.1143079495986134</v>
       </c>
       <c r="W90">
-        <v>0.177586133762878</v>
+        <v>0.1778469637205984</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.5780345178566246</v>
+        <v>0.5715397479930671</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2188249293654341</v>
+        <v>0.2203749293654341</v>
       </c>
       <c r="C91">
-        <v>-14.29138149040749</v>
+        <v>-14.6904700805167</v>
       </c>
       <c r="D91">
-        <v>11.04761850959251</v>
+        <v>10.94952991948331</v>
       </c>
       <c r="E91">
-        <v>14.189</v>
+        <v>14.49</v>
       </c>
       <c r="F91">
-        <v>26.789</v>
+        <v>27.09</v>
       </c>
       <c r="G91">
         <v>1.45</v>
@@ -8749,37 +8749,37 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M91">
-        <v>5.3792312</v>
+        <v>5.439672000000001</v>
       </c>
       <c r="N91">
-        <v>-2.304786755555556</v>
+        <v>-2.365227555555557</v>
       </c>
       <c r="O91">
-        <v>-0.4609573511111113</v>
+        <v>-0.4730455111111114</v>
       </c>
       <c r="P91">
-        <v>-1.843829404444445</v>
+        <v>-1.892182044444445</v>
       </c>
       <c r="Q91">
-        <v>-0.8738294044444448</v>
+        <v>-0.9221820444444451</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.5503739241281954</v>
+        <v>0.6008313165410151</v>
       </c>
       <c r="T91">
-        <v>5.525291281908042</v>
+        <v>6.077820410098847</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.1143079495986134</v>
+        <v>0.1130378612697399</v>
       </c>
       <c r="W91">
-        <v>0.1778469637205984</v>
+        <v>0.1781019974570362</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.5715397479930671</v>
+        <v>0.5651893063486997</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2203749293654341</v>
+        <v>0.2219249293654341</v>
       </c>
       <c r="C92">
-        <v>-14.6904700805167</v>
+        <v>-15.08783219936237</v>
       </c>
       <c r="D92">
-        <v>10.94952991948331</v>
+        <v>10.85316780063763</v>
       </c>
       <c r="E92">
-        <v>14.49</v>
+        <v>14.791</v>
       </c>
       <c r="F92">
-        <v>27.09</v>
+        <v>27.391</v>
       </c>
       <c r="G92">
         <v>1.45</v>
@@ -8831,37 +8831,37 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M92">
-        <v>5.439672000000001</v>
+        <v>5.5001128</v>
       </c>
       <c r="N92">
-        <v>-2.365227555555557</v>
+        <v>-2.425668355555556</v>
       </c>
       <c r="O92">
-        <v>-0.4730455111111114</v>
+        <v>-0.4851336711111112</v>
       </c>
       <c r="P92">
-        <v>-1.892182044444445</v>
+        <v>-1.940534684444445</v>
       </c>
       <c r="Q92">
-        <v>-0.9221820444444451</v>
+        <v>-0.9705346844444447</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6008313165410151</v>
+        <v>0.6625014628233501</v>
       </c>
       <c r="T92">
-        <v>6.077820410098847</v>
+        <v>6.75313378899872</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.1130378612697399</v>
+        <v>0.1117956869700725</v>
       </c>
       <c r="W92">
-        <v>0.1781019974570362</v>
+        <v>0.1783514260564094</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.5651893063486997</v>
+        <v>0.5589784348503624</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2219249293654341</v>
+        <v>0.2234749293654341</v>
       </c>
       <c r="C93">
-        <v>-15.08783219936237</v>
+        <v>-15.48351303109857</v>
       </c>
       <c r="D93">
-        <v>10.85316780063763</v>
+        <v>10.75848696890144</v>
       </c>
       <c r="E93">
-        <v>14.791</v>
+        <v>15.092</v>
       </c>
       <c r="F93">
-        <v>27.391</v>
+        <v>27.692</v>
       </c>
       <c r="G93">
         <v>1.45</v>
@@ -8913,37 +8913,37 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M93">
-        <v>5.5001128</v>
+        <v>5.560553600000001</v>
       </c>
       <c r="N93">
-        <v>-2.425668355555556</v>
+        <v>-2.486109155555557</v>
       </c>
       <c r="O93">
-        <v>-0.4851336711111112</v>
+        <v>-0.4972218311111115</v>
       </c>
       <c r="P93">
-        <v>-1.940534684444445</v>
+        <v>-1.988887324444446</v>
       </c>
       <c r="Q93">
-        <v>-0.9705346844444447</v>
+        <v>-1.018887324444446</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.6625014628233501</v>
+        <v>0.7395891456762691</v>
       </c>
       <c r="T93">
-        <v>6.75313378899872</v>
+        <v>7.597275512623562</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.1117956869700725</v>
+        <v>0.1105805164595282</v>
       </c>
       <c r="W93">
-        <v>0.1783514260564094</v>
+        <v>0.1785954322949267</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.5589784348503624</v>
+        <v>0.5529025822976409</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2234749293654341</v>
+        <v>0.2250249293654342</v>
       </c>
       <c r="C94">
-        <v>-15.48351303109857</v>
+        <v>-15.8775561968057</v>
       </c>
       <c r="D94">
-        <v>10.75848696890144</v>
+        <v>10.6654438031943</v>
       </c>
       <c r="E94">
-        <v>15.092</v>
+        <v>15.393</v>
       </c>
       <c r="F94">
-        <v>27.692</v>
+        <v>27.993</v>
       </c>
       <c r="G94">
         <v>1.45</v>
@@ -8995,37 +8995,37 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M94">
-        <v>5.560553600000001</v>
+        <v>5.620994400000001</v>
       </c>
       <c r="N94">
-        <v>-2.486109155555557</v>
+        <v>-2.546549955555557</v>
       </c>
       <c r="O94">
-        <v>-0.4972218311111115</v>
+        <v>-0.5093099911111113</v>
       </c>
       <c r="P94">
-        <v>-1.988887324444446</v>
+        <v>-2.037239964444445</v>
       </c>
       <c r="Q94">
-        <v>-1.018887324444446</v>
+        <v>-1.067239964444445</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7395891456762691</v>
+        <v>0.8387018807728792</v>
       </c>
       <c r="T94">
-        <v>7.597275512623562</v>
+        <v>8.682600585855502</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.1105805164595282</v>
+        <v>0.1093914786481354</v>
       </c>
       <c r="W94">
-        <v>0.1785954322949267</v>
+        <v>0.1788341910874544</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.5529025822976409</v>
+        <v>0.546957393240677</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2250249293654342</v>
+        <v>0.2265749293654341</v>
       </c>
       <c r="C95">
-        <v>-15.8775561968057</v>
+        <v>-16.27000382150112</v>
       </c>
       <c r="D95">
-        <v>10.6654438031943</v>
+        <v>10.57399617849889</v>
       </c>
       <c r="E95">
-        <v>15.393</v>
+        <v>15.694</v>
       </c>
       <c r="F95">
-        <v>27.993</v>
+        <v>28.294</v>
       </c>
       <c r="G95">
         <v>1.45</v>
@@ -9077,37 +9077,37 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M95">
-        <v>5.620994400000001</v>
+        <v>5.681435200000001</v>
       </c>
       <c r="N95">
-        <v>-2.546549955555557</v>
+        <v>-2.606990755555557</v>
       </c>
       <c r="O95">
-        <v>-0.5093099911111113</v>
+        <v>-0.5213981511111114</v>
       </c>
       <c r="P95">
-        <v>-2.037239964444445</v>
+        <v>-2.085592604444446</v>
       </c>
       <c r="Q95">
-        <v>-1.067239964444445</v>
+        <v>-1.115592604444446</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.8387018807728792</v>
+        <v>0.9708521942350259</v>
       </c>
       <c r="T95">
-        <v>8.682600585855502</v>
+        <v>10.12970068349809</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.1093914786481354</v>
+        <v>0.1082277395135808</v>
       </c>
       <c r="W95">
-        <v>0.1788341910874544</v>
+        <v>0.179067869905673</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.546957393240677</v>
+        <v>0.5411386975679039</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2265749293654341</v>
+        <v>0.2281249293654342</v>
       </c>
       <c r="C96">
-        <v>-16.27000382150112</v>
+        <v>-16.66089659773154</v>
       </c>
       <c r="D96">
-        <v>10.57399617849889</v>
+        <v>10.48410340226847</v>
       </c>
       <c r="E96">
-        <v>15.694</v>
+        <v>15.995</v>
       </c>
       <c r="F96">
-        <v>28.294</v>
+        <v>28.595</v>
       </c>
       <c r="G96">
         <v>1.45</v>
@@ -9159,37 +9159,37 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M96">
-        <v>5.681435200000001</v>
+        <v>5.741876</v>
       </c>
       <c r="N96">
-        <v>-2.606990755555557</v>
+        <v>-2.667431555555556</v>
       </c>
       <c r="O96">
-        <v>-0.5213981511111114</v>
+        <v>-0.5334863111111113</v>
       </c>
       <c r="P96">
-        <v>-2.085592604444446</v>
+        <v>-2.133945244444445</v>
       </c>
       <c r="Q96">
-        <v>-1.115592604444446</v>
+        <v>-1.163945244444445</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.9708521942350259</v>
+        <v>1.155862633082032</v>
       </c>
       <c r="T96">
-        <v>10.12970068349809</v>
+        <v>12.15564082019771</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.1082277395135808</v>
+        <v>0.1070885001502799</v>
       </c>
       <c r="W96">
-        <v>0.179067869905673</v>
+        <v>0.1792966291698238</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.5411386975679039</v>
+        <v>0.5354425007513997</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2281249293654342</v>
+        <v>0.2296749293654341</v>
       </c>
       <c r="C97">
-        <v>-16.66089659773154</v>
+        <v>-17.0502738459491</v>
       </c>
       <c r="D97">
-        <v>10.48410340226847</v>
+        <v>10.3957261540509</v>
       </c>
       <c r="E97">
-        <v>15.995</v>
+        <v>16.29600000000001</v>
       </c>
       <c r="F97">
-        <v>28.595</v>
+        <v>28.896</v>
       </c>
       <c r="G97">
         <v>1.45</v>
@@ -9241,37 +9241,37 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M97">
-        <v>5.741876</v>
+        <v>5.802316800000001</v>
       </c>
       <c r="N97">
-        <v>-2.667431555555556</v>
+        <v>-2.727872355555557</v>
       </c>
       <c r="O97">
-        <v>-0.5334863111111113</v>
+        <v>-0.5455744711111113</v>
       </c>
       <c r="P97">
-        <v>-2.133945244444445</v>
+        <v>-2.182297884444445</v>
       </c>
       <c r="Q97">
-        <v>-1.163945244444445</v>
+        <v>-1.212297884444445</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.155862633082032</v>
+        <v>1.43337829135254</v>
       </c>
       <c r="T97">
-        <v>12.15564082019771</v>
+        <v>15.19455102524714</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.1070885001502799</v>
+        <v>0.1059729949403812</v>
       </c>
       <c r="W97">
-        <v>0.1792966291698238</v>
+        <v>0.1795206226159715</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.5354425007513997</v>
+        <v>0.529864974701906</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2296749293654341</v>
+        <v>0.2312249293654342</v>
       </c>
       <c r="C98">
-        <v>-17.05027384594909</v>
+        <v>-17.43817357185932</v>
       </c>
       <c r="D98">
-        <v>10.39572615405091</v>
+        <v>10.30882642814068</v>
       </c>
       <c r="E98">
-        <v>16.296</v>
+        <v>16.597</v>
       </c>
       <c r="F98">
-        <v>28.896</v>
+        <v>29.197</v>
       </c>
       <c r="G98">
         <v>1.45</v>
@@ -9323,37 +9323,37 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M98">
-        <v>5.802316800000001</v>
+        <v>5.8627576</v>
       </c>
       <c r="N98">
-        <v>-2.727872355555557</v>
+        <v>-2.788313155555556</v>
       </c>
       <c r="O98">
-        <v>-0.5455744711111113</v>
+        <v>-0.5576626311111113</v>
       </c>
       <c r="P98">
-        <v>-2.182297884444445</v>
+        <v>-2.230650524444445</v>
       </c>
       <c r="Q98">
-        <v>-1.212297884444445</v>
+        <v>-1.260650524444445</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.433378291352536</v>
+        <v>1.895904388470049</v>
       </c>
       <c r="T98">
-        <v>15.1945510252471</v>
+        <v>20.25940136699614</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.1059729949403812</v>
+        <v>0.104880489837903</v>
       </c>
       <c r="W98">
-        <v>0.1795206226159715</v>
+        <v>0.1797399976405491</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.529864974701906</v>
+        <v>0.5244024491895152</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2312249293654342</v>
+        <v>0.2327749293654341</v>
       </c>
       <c r="C99">
-        <v>-17.43817357185932</v>
+        <v>-17.82463252091654</v>
       </c>
       <c r="D99">
-        <v>10.30882642814068</v>
+        <v>10.22336747908346</v>
       </c>
       <c r="E99">
-        <v>16.597</v>
+        <v>16.898</v>
       </c>
       <c r="F99">
-        <v>29.197</v>
+        <v>29.498</v>
       </c>
       <c r="G99">
         <v>1.45</v>
@@ -9405,37 +9405,37 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M99">
-        <v>5.8627576</v>
+        <v>5.9231984</v>
       </c>
       <c r="N99">
-        <v>-2.788313155555556</v>
+        <v>-2.848753955555556</v>
       </c>
       <c r="O99">
-        <v>-0.5576626311111113</v>
+        <v>-0.5697507911111113</v>
       </c>
       <c r="P99">
-        <v>-2.230650524444445</v>
+        <v>-2.279003164444445</v>
       </c>
       <c r="Q99">
-        <v>-1.260650524444445</v>
+        <v>-1.309003164444445</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.895904388470049</v>
+        <v>2.820956582705072</v>
       </c>
       <c r="T99">
-        <v>20.25940136699614</v>
+        <v>30.3891020504942</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.104880489837903</v>
+        <v>0.1038102807579244</v>
       </c>
       <c r="W99">
-        <v>0.1797399976405491</v>
+        <v>0.1799548956238088</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.5244024491895152</v>
+        <v>0.5190514037896221</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2327749293654341</v>
+        <v>0.2343249293654341</v>
       </c>
       <c r="C100">
-        <v>-17.82463252091654</v>
+        <v>-18.2096862301311</v>
       </c>
       <c r="D100">
-        <v>10.22336747908346</v>
+        <v>10.1393137698689</v>
       </c>
       <c r="E100">
-        <v>16.898</v>
+        <v>17.199</v>
       </c>
       <c r="F100">
-        <v>29.498</v>
+        <v>29.799</v>
       </c>
       <c r="G100">
         <v>1.45</v>
@@ -9487,37 +9487,37 @@
         <v>3.074444444444444</v>
       </c>
       <c r="M100">
-        <v>5.9231984</v>
+        <v>5.9836392</v>
       </c>
       <c r="N100">
-        <v>-2.848753955555556</v>
+        <v>-2.909194755555556</v>
       </c>
       <c r="O100">
-        <v>-0.5697507911111113</v>
+        <v>-0.5818389511111112</v>
       </c>
       <c r="P100">
-        <v>-2.279003164444445</v>
+        <v>-2.327355804444445</v>
       </c>
       <c r="Q100">
-        <v>-1.309003164444445</v>
+        <v>-1.357355804444444</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.820956582705072</v>
+        <v>5.596113165410145</v>
       </c>
       <c r="T100">
-        <v>30.3891020504942</v>
+        <v>60.7782041009884</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.1038102807579244</v>
+        <v>0.1027616920634</v>
       </c>
       <c r="W100">
-        <v>0.1799548956238088</v>
+        <v>0.1801654522336693</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.5190514037896221</v>
+        <v>0.5138084603169998</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2343249293654341</v>
-      </c>
-      <c r="C101">
-        <v>-18.2096862301311</v>
-      </c>
-      <c r="D101">
-        <v>10.1393137698689</v>
-      </c>
-      <c r="E101">
-        <v>17.199</v>
-      </c>
-      <c r="F101">
-        <v>29.799</v>
-      </c>
-      <c r="G101">
-        <v>1.45</v>
-      </c>
-      <c r="H101">
-        <v>17.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>4.044444444444444</v>
-      </c>
-      <c r="K101">
-        <v>0.9700000000000002</v>
-      </c>
-      <c r="L101">
-        <v>3.074444444444444</v>
-      </c>
-      <c r="M101">
-        <v>5.9836392</v>
-      </c>
-      <c r="N101">
-        <v>-2.909194755555556</v>
-      </c>
-      <c r="O101">
-        <v>-0.5818389511111112</v>
-      </c>
-      <c r="P101">
-        <v>-2.327355804444445</v>
-      </c>
-      <c r="Q101">
-        <v>-1.357355804444444</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>5.596113165410145</v>
-      </c>
-      <c r="T101">
-        <v>60.7782041009884</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.1027616920634</v>
-      </c>
-      <c r="W101">
-        <v>0.1801654522336693</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.5138084603169998</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
